--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_synthesis.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_synthesis.xlsx
@@ -1,34 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+  <fileSharing readOnlyRecommended="0" userName="dabin"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="28800" windowHeight="12375" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="cfg_synthesis" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="cfg_synthesis" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext uri="smNativeData">
+      <pm:revision xmlns:pm="smNativeData" day="1789641695" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1789641695" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1789641695" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1789641695"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="336">
   <si>
     <t>配方ID#客户端#C</t>
   </si>
@@ -408,15 +404,15 @@
     <t>0#0</t>
   </si>
   <si>
+    <t>装备追加</t>
+  </si>
+  <si>
+    <t>请放入想追加的装备</t>
+  </si>
+  <si>
     <t>1254004099#1000</t>
   </si>
   <si>
-    <t>装备追加</t>
-  </si>
-  <si>
-    <t>请放入想追加的装备</t>
-  </si>
-  <si>
     <t>600076156#1#100</t>
   </si>
   <si>
@@ -606,7 +602,7 @@
     <t>10010002#1000000</t>
   </si>
   <si>
-    <t>2132001199#1#100#600076127|2132002199#1#100#600076129|2132003199#1#100#600076131|2137002199#1#100#</t>
+    <t>2132001199#1#100#600076127|2132002199#1#100#600076129|2132003199#1#100#600076131|2132004199#1#100#|2132005199#1#100#|2137002199#1#100#</t>
   </si>
   <si>
     <t>2代翅膀</t>
@@ -651,7 +647,7 @@
     <t>10010002#20000000</t>
   </si>
   <si>
-    <t>21340011#1#10099|21340021#1#10099|21340031#1#10099</t>
+    <t>2134001199#1#100|2134002199#1#100|2134003199#1#100|2134004199#1#100|2134005199#1#100</t>
   </si>
   <si>
     <t>4代翅膀</t>
@@ -867,10 +863,10 @@
     <t>守护/破坏炎狼兽之角\n祝福宝石\n灵魂宝石\n玛雅之石</t>
   </si>
   <si>
-    <t>1#1160010599#1|1#1253000299#5|1#1253000399#5|1#1253000199#5</t>
-  </si>
-  <si>
-    <t>1#1160010699#1|1#1253000299#5|1#1253000399#5|1#1253000199#5</t>
+    <t>1#1160010599#1|1#1253000299#66|1#1253000399#66|1#1253000199#5</t>
+  </si>
+  <si>
+    <t>1#1160010699#1|1#1253000299#66|1#1253000399#66|1#1253000199#5</t>
   </si>
   <si>
     <t>1160001999#1#100</t>
@@ -882,7 +878,7 @@
     <t>白毛狮王\n祝福宝石\n灵魂宝石\n玛雅之石\n生命宝石</t>
   </si>
   <si>
-    <t>1#1160004399#1|1#1253000299#20|1#1253000399#20|1#1253000199#20|1#1253000499#5</t>
+    <t>1#1160004399#1|1#1253000299#99|1#1253000399#99|1#1253000199#20|1#1253000499#5</t>
   </si>
   <si>
     <t>1160003099#1#100</t>
@@ -894,7 +890,10 @@
     <t>金龙爪\n祝福宝石\n灵魂宝石\n玛雅之石\n生命宝石</t>
   </si>
   <si>
-    <t>1#1160001999#1|1#1253000299#50|1#1253000399#50|1#1253000199#50|1#1253000499#10</t>
+    <t>1#1160001999#1|1#1253000299#99|1#1253000399#99|1#1253000199#50|1#1253000499#10</t>
+  </si>
+  <si>
+    <t>2132006199#1#100</t>
   </si>
   <si>
     <t>王者披风</t>
@@ -996,7 +995,7 @@
     <t>斯提克斯精工模具\n二代耳环\n祝福宝石\n灵魂宝石\n创造宝石\n玛雅之石</t>
   </si>
   <si>
-    <t>2#11#0#99#0#2120020199#1|1#1253000199#40|1#1253000299#40|1#1253000399#40|1#1253000599#30|1254010499#5</t>
+    <t>3#0#0#99#0#9#2120020199#1|1#1253000199#200|1#1253000299#66|1#1253000399#66|1#1253000599#200|1254010499#5</t>
   </si>
   <si>
     <t>2120031199#1#100</t>
@@ -1005,7 +1004,7 @@
     <t>赫鲁斯之耀</t>
   </si>
   <si>
-    <t>2#11#0#99#0#2120021199#1|1#1253000199#40|1#1253000299#40|1#1253000399#40|1#1253000599#30|1254010499#5</t>
+    <t>3#0#0#99#0#9#2120021199#1|1#1253000199#200|1#1253000299#66|1#1253000399#66|1#1253000599#200|1254010499#5</t>
   </si>
   <si>
     <t>1180000199#1#40</t>
@@ -1020,7 +1019,7 @@
     <t>天鹰兽之灵魂\n祝福宝石\n灵魂宝石\n玛雅之石\n创造宝石\n生命宝石</t>
   </si>
   <si>
-    <t>1#1254005099#1|1#1253000299#1|1#1253000399#1|1#1253000199#1|1#1253000599#1|1#1253000499#2</t>
+    <t>1#1254005099#1|1#1253000299#99|1#1253000399#99|1#1253000199#666|1#1253000599#666|1#1253000499#6</t>
   </si>
   <si>
     <t>1190000199#1#40</t>
@@ -1036,6 +1035,45 @@
   </si>
   <si>
     <t>1#1254005199#1|1#1253000299#1|1#1253000399#1|1#1253000199#1|1#1253000599#1|1#1253000499#2</t>
+  </si>
+  <si>
+    <t>2000000299#1#100</t>
+  </si>
+  <si>
+    <t>葬月战旗</t>
+  </si>
+  <si>
+    <t>奔雷战旗\n祝福宝石\n灵魂宝石\n玛雅之石\n生命宝石</t>
+  </si>
+  <si>
+    <t>1#2000000199#2|1#1253000299#66|1#1253000399#66|1#1253000199#66|1#1253000499#3</t>
+  </si>
+  <si>
+    <t>2000000399#1#100</t>
+  </si>
+  <si>
+    <t>凌乾战旗</t>
+  </si>
+  <si>
+    <t>葬月战旗\n祝福宝石\n灵魂宝石\n玛雅之石\n生命宝石</t>
+  </si>
+  <si>
+    <t>1#2000000299#2|1#1253000299#88|1#1253000399#88|1#1253000199#88|1#1253000499#5</t>
+  </si>
+  <si>
+    <t>2000000499#1#100</t>
+  </si>
+  <si>
+    <t>御荒战旗</t>
+  </si>
+  <si>
+    <t>凌乾战旗\n祝福宝石\n灵魂宝石\n玛雅之石\n生命宝石</t>
+  </si>
+  <si>
+    <t>1#2000000399#2|1#1253000299#99|1#1253000399#99|1#1253000199#99|1#1253000499#10</t>
+  </si>
+  <si>
+    <t>|1#50088887#100</t>
   </si>
   <si>
     <t>2132001199#1#17#600076127|2132002199#1#17#600076129|2132003199#1#17#600076131|2137004199#1#17#|2137005199#1#17#|2137002199#1#17#</t>
@@ -1050,179 +1088,367 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="13">
+    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="9" formatCode="0%"/>
   </numFmts>
   <fonts count="22">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789641695" ulstyle="none" kern="1">
+            <pm:latin face="宋体" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789641695" ulstyle="none" kern="1">
+            <pm:latin face="Arial" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
+    </font>
+    <font>
       <name val="微软雅黑"/>
       <charset val="134"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789641695" ulstyle="none" kern="1">
+            <pm:latin face="微软雅黑" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <sz val="10.5"/>
+      <name val="Consolas"/>
+      <family val="3"/>
       <color rgb="FFFFA657"/>
-      <name val="Consolas"/>
-      <charset val="134"/>
+      <sz val="10.50"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789641695" fgClr="FFA657" ulstyle="none" kern="1">
+            <pm:latin face="Consolas" sz="210" lang="default"/>
+            <pm:cs face="Times New Roman" sz="210" lang="default"/>
+            <pm:ea face="SimSun" sz="210" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <u/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color rgb="FF0000FF"/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <u val="single"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789641695" fgClr="0000FF" ulstyle="single" kern="1">
+            <pm:latin face="宋体" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <u/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color rgb="FF800080"/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <u val="single"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789641695" fgClr="800080" ulstyle="single" kern="1">
+            <pm:latin face="宋体" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color rgb="FFFF0000"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789641695" fgClr="FF0000" ulstyle="none" kern="1">
+            <pm:latin face="宋体" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <b/>
+      <color rgb="FF44546A"/>
+      <sz val="18"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789641695" fgClr="44546A" ulstyle="none" kern="1">
+            <pm:latin face="宋体" sz="360" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="360" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="360" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <i/>
+      <color rgb="FF7F7F7F"/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789641695" fgClr="7F7F7F" ulstyle="none" kern="1">
+            <pm:latin face="宋体" sz="220" lang="default" i="1"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default" i="1"/>
+            <pm:ea face="SimSun" sz="220" lang="default" i="1"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <b/>
+      <color rgb="FF44546A"/>
+      <sz val="15"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789641695" fgClr="44546A" ulstyle="none" kern="1">
+            <pm:latin face="宋体" sz="300" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="300" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="300" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <b/>
+      <color rgb="FF44546A"/>
+      <sz val="13"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789641695" fgClr="44546A" ulstyle="none" kern="1">
+            <pm:latin face="宋体" sz="260" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="260" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="260" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <b/>
+      <color rgb="FF44546A"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789641695" fgClr="44546A" ulstyle="none" kern="1">
+            <pm:latin face="宋体" sz="220" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color rgb="FF3F3F76"/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789641695" fgClr="3F3F76" ulstyle="none" kern="1">
+            <pm:latin face="宋体" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b/>
+      <color rgb="FF3F3F3F"/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789641695" fgClr="3F3F3F" ulstyle="none" kern="1">
+            <pm:latin face="宋体" sz="220" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b/>
+      <color rgb="FFFA7D00"/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789641695" fgClr="FA7D00" ulstyle="none" kern="1">
+            <pm:latin face="宋体" sz="220" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789641695" fgClr="FFFFFF" ulstyle="none" kern="1">
+            <pm:latin face="宋体" sz="220" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color rgb="FFFA7D00"/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789641695" fgClr="FA7D00" ulstyle="none" kern="1">
+            <pm:latin face="宋体" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789641695" ulstyle="none" kern="1">
+            <pm:latin face="宋体" sz="220" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789641695" fgClr="006100" ulstyle="none" kern="1">
+            <pm:latin face="宋体" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789641695" fgClr="9C0006" ulstyle="none" kern="1">
+            <pm:latin face="宋体" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789641695" fgClr="9C6500" ulstyle="none" kern="1">
+            <pm:latin face="宋体" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789641695" fgClr="FFFFFF" ulstyle="none" kern="1">
+            <pm:latin face="宋体" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1231,204 +1457,399 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00FFFFCC" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00FFCC99" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00F2F2F2" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00F2F2F2" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00A5A5A5" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00C6EFCE" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00FFC7CE" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00FFEB9C" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5B9BD5"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00DDEBF7" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BC2E6"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="009BC2E6" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED7D31"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00ED7D31" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE3D5"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00FBE3D5" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8CAAB"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00F8CAAB" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4AF82"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00F4AF82" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00A5A5A5" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBEBEB"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00EBEBEB" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00D9D9D9" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7C7C7"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00C7C7C7" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00FFC000" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CA"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00FFF2CA" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE697"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD964"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00FFD964" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="004472C4" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00D9E1F2" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4C6E7"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00B4C6E7" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8EA9DB"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="008EA9DB" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70AD47"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="0070AD47" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1EFD8"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00E1EFD8" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5DFB3"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00C5DFB3" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8D08C"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00A8D08C" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="100" fgClr="00FFFF00" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="38">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
@@ -1443,25 +1864,58 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="B2B2B2"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="B2B2B2"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="B2B2B2"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="B2B2B2"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="medium">
-        <color theme="4"/>
+        <color rgb="FF5B9BD5"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695">
+            <pm:line position="bottom" type="1" style="0" width="30" dist="20" width2="20" rgb="5B9BD5"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color rgb="FFACCCEA"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695">
+            <pm:line position="bottom" type="1" style="0" width="30" dist="20" width2="20" rgb="ACCCEA"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
@@ -1476,7 +1930,16 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
@@ -1491,7 +1954,40 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="double">
@@ -1506,491 +2002,1243 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695">
+            <pm:line position="top" type="2" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
+            <pm:line position="bottom" type="2" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
+            <pm:line position="left" type="2" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
+            <pm:line position="right" type="2" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695">
+            <pm:line position="bottom" type="2" style="0" width="20" dist="20" width2="20" rgb="FF8001"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF5B9BD5"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF5B9BD5"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="5B9BD5"/>
+            <pm:line position="bottom" type="2" style="0" width="20" dist="20" width2="20" rgb="5B9BD5"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789641695"/>
+        </ext>
+      </extLst>
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="19" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="22" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="23" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="24" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="25" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="26" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="27" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="28" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="29" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="30" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="31" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="32" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="33" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="34" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="35" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="36" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="13">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="14">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="15">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="16">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="17">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="18">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" xfId="19">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="20">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="21">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="10" xfId="22">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="11" xfId="23">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="12" xfId="24">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="13" xfId="25">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="14" xfId="26">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="15" xfId="27">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="16" xfId="28">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="17" xfId="29">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="18" xfId="30">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="19" xfId="31">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="20" xfId="32">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="21" xfId="33">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="22" xfId="34">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="23" xfId="35">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="24" xfId="36">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="25" xfId="37">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="26" xfId="38">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="27" xfId="39">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="28" xfId="40">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="29" xfId="41">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="30" xfId="42">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="31" xfId="43">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="32" xfId="44">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="33" xfId="45">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="34" xfId="46">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="35" xfId="47">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="36" xfId="48">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="35" borderId="34" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="37" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3" customBuiltin="1"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4" customBuiltin="1"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5" customBuiltin="1"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6" customBuiltin="1"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8" customBuiltin="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9" customBuiltin="1"/>
+    <cellStyle name="Note" xfId="8" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="10" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="16" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="17" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="21" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="22" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:charSpec xmlns:pm="smNativeData" id="1789641695" fgClr="9C0006">
+              <pm:latin/>
+              <pm:cs/>
+              <pm:ea/>
+            </pm:charSpec>
+          </ext>
+        </extLst>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+          <extLst>
+            <ext uri="smNativeData">
+              <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="0" fgClr="00000000" bgLvl="100" bgClr="00FFC7CE"/>
+            </ext>
+          </extLst>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFF9900"/>
+          <extLst>
+            <ext uri="smNativeData">
+              <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="0" fgClr="00000000" bgLvl="100" bgClr="00FF9900"/>
+            </ext>
+          </extLst>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:charSpec xmlns:pm="smNativeData" id="1789641695" fgClr="9C0006">
+              <pm:latin/>
+              <pm:cs/>
+              <pm:ea/>
+            </pm:charSpec>
+          </ext>
+        </extLst>
       </font>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
+          <extLst>
+            <ext uri="smNativeData">
+              <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="0" fgClr="00000000" bgLvl="100" bgClr="00FFC7CE"/>
+            </ext>
+          </extLst>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <bgColor rgb="FFFF9900"/>
+          <extLst>
+            <ext uri="smNativeData">
+              <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="0" fgClr="00000000" bgLvl="100" bgClr="00FF9900"/>
+            </ext>
+          </extLst>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:charSpec xmlns:pm="smNativeData" id="1789641695" fgClr="9C0006">
+              <pm:latin/>
+              <pm:cs/>
+              <pm:ea/>
+            </pm:charSpec>
+          </ext>
+        </extLst>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+          <extLst>
+            <ext uri="smNativeData">
+              <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="0" fgClr="00000000" bgLvl="100" bgClr="00FFC7CE"/>
+            </ext>
+          </extLst>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <bgColor rgb="FFFF9900"/>
+          <extLst>
+            <ext uri="smNativeData">
+              <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="0" fgClr="00000000" bgLvl="100" bgClr="00FF9900"/>
+            </ext>
+          </extLst>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
+        <color rgb="FF9C0006"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:charSpec xmlns:pm="smNativeData" id="1789641695" fgClr="9C0006">
+              <pm:latin/>
+              <pm:cs/>
+              <pm:ea/>
+            </pm:charSpec>
+          </ext>
+        </extLst>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <bgColor rgb="FFFFC7CE"/>
+          <extLst>
+            <ext uri="smNativeData">
+              <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="0" fgClr="00000000" bgLvl="100" bgClr="00FFC7CE"/>
+            </ext>
+          </extLst>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <bgColor rgb="FFFF9900"/>
+          <extLst>
+            <ext uri="smNativeData">
+              <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="0" fgClr="00000000" bgLvl="100" bgClr="00FF9900"/>
+            </ext>
+          </extLst>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
-        <color theme="1"/>
+        <color rgb="FF9C0006"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:charSpec xmlns:pm="smNativeData" id="1789641695" fgClr="9C0006">
+              <pm:latin/>
+              <pm:cs/>
+              <pm:ea/>
+            </pm:charSpec>
+          </ext>
+        </extLst>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <bgColor rgb="FFFFC7CE"/>
+          <extLst>
+            <ext uri="smNativeData">
+              <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="0" fgClr="00000000" bgLvl="100" bgClr="00FFC7CE"/>
+            </ext>
+          </extLst>
         </patternFill>
       </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+          <extLst>
+            <ext uri="smNativeData">
+              <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="0" fgClr="00000000" bgLvl="100" bgClr="00FF9900"/>
+            </ext>
+          </extLst>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
-        <color theme="1"/>
+        <color rgb="FF9C0006"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:charSpec xmlns:pm="smNativeData" id="1789641695" fgClr="9C0006">
+              <pm:latin/>
+              <pm:cs/>
+              <pm:ea/>
+            </pm:charSpec>
+          </ext>
+        </extLst>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <bgColor rgb="FFFFC7CE"/>
+          <extLst>
+            <ext uri="smNativeData">
+              <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="0" fgClr="00000000" bgLvl="100" bgClr="00FFC7CE"/>
+            </ext>
+          </extLst>
         </patternFill>
       </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+          <extLst>
+            <ext uri="smNativeData">
+              <pm:shade xmlns:pm="smNativeData" id="1789641695" type="1" fgLvl="0" fgClr="00000000" bgLvl="100" bgClr="00FF9900"/>
+            </ext>
+          </extLst>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="8"/>
-      <tableStyleElement type="headerRow" dxfId="7"/>
-      <tableStyleElement type="totalRow" dxfId="6"/>
-      <tableStyleElement type="firstColumn" dxfId="5"/>
-      <tableStyleElement type="lastColumn" dxfId="4"/>
-      <tableStyleElement type="firstRowStripe" dxfId="3"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="2"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="18"/>
-      <tableStyleElement type="totalRow" dxfId="17"/>
-      <tableStyleElement type="firstRowStripe" dxfId="16"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="15"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="14"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="13"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="12"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="11"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="10"/>
-      <tableStyleElement type="pageFieldValues" dxfId="9"/>
-    </tableStyle>
-  </tableStyles>
+  <tableStyles count="0"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="smNativeData">
+      <pm:charStyles xmlns:pm="smNativeData" id="1789641695" count="1">
+        <pm:charStyle name="普通" fontId="0" Id="1"/>
+      </pm:charStyles>
+      <pm:colors xmlns:pm="smNativeData" id="1789641695" count="44">
+        <pm:color name="颜色 24" rgb="FFA657"/>
+        <pm:color name="颜色 25" rgb="800080"/>
+        <pm:color name="颜色 26" rgb="44546A"/>
+        <pm:color name="颜色 27" rgb="3F3F76"/>
+        <pm:color name="颜色 28" rgb="3F3F3F"/>
+        <pm:color name="颜色 29" rgb="FA7D00"/>
+        <pm:color name="颜色 30" rgb="006100"/>
+        <pm:color name="颜色 31" rgb="9C0006"/>
+        <pm:color name="颜色 32" rgb="9C6500"/>
+        <pm:color name="颜色 33" rgb="E1EFD8"/>
+        <pm:color name="20% 灰色" rgb="000000"/>
+        <pm:color name="颜色 35" rgb="FFFFCC"/>
+        <pm:color name="颜色 36" rgb="FFCC99"/>
+        <pm:color name="颜色 37" rgb="F2F2F2"/>
+        <pm:color name="颜色 38" rgb="A5A5A5"/>
+        <pm:color name="颜色 39" rgb="C6EFCE"/>
+        <pm:color name="颜色 40" rgb="FFC7CE"/>
+        <pm:color name="颜色 41" rgb="FFEB9C"/>
+        <pm:color name="颜色 42" rgb="5B9BD5"/>
+        <pm:color name="颜色 43" rgb="DDEBF7"/>
+        <pm:color name="颜色 44" rgb="BDD7EE"/>
+        <pm:color name="颜色 45" rgb="9BC2E6"/>
+        <pm:color name="颜色 46" rgb="ED7D31"/>
+        <pm:color name="颜色 47" rgb="FBE3D5"/>
+        <pm:color name="颜色 48" rgb="F8CAAB"/>
+        <pm:color name="颜色 49" rgb="F4AF82"/>
+        <pm:color name="颜色 50" rgb="EBEBEB"/>
+        <pm:color name="颜色 51" rgb="D9D9D9"/>
+        <pm:color name="颜色 52" rgb="C7C7C7"/>
+        <pm:color name="颜色 53" rgb="FFC000"/>
+        <pm:color name="颜色 54" rgb="FFF2CA"/>
+        <pm:color name="颜色 55" rgb="FFE697"/>
+        <pm:color name="颜色 56" rgb="FFD964"/>
+        <pm:color name="颜色 57" rgb="4472C4"/>
+        <pm:color name="颜色 58" rgb="D9E1F2"/>
+        <pm:color name="颜色 59" rgb="B4C6E7"/>
+        <pm:color name="颜色 60" rgb="8EA9DB"/>
+        <pm:color name="颜色 61" rgb="70AD47"/>
+        <pm:color name="颜色 62" rgb="C5DFB3"/>
+        <pm:color name="颜色 63" rgb="A8D08C"/>
+        <pm:color name="颜色 64" rgb="B2B2B2"/>
+        <pm:color name="颜色 65" rgb="ACCCEA"/>
+        <pm:color name="颜色 66" rgb="FF8001"/>
+        <pm:color name="颜色 67" rgb="FF9900"/>
+      </pm:colors>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2000,106 +3248,46 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="EEECE1"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="1F497D"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="宋体"/>
+        <a:ea typeface="SimSun"/>
+        <a:cs typeface="Times New Roman"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2111,166 +3299,224 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr>
+        <a:prstTxWarp prst="textNoShape">
+          <a:avLst/>
+        </a:prstTxWarp>
+        <a:noAutofit/>
+      </a:bodyPr>
+      <a:lstStyle>
+        <a:defPPr>
+          <a:defRPr/>
+        </a:defPPr>
+      </a:lstStyle>
+      <a:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:AJ58"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <dimension ref="A1:AJ61"/>
+  <sheetFormatPr defaultRowHeight="14.50"/>
   <cols>
-    <col min="2" max="2" width="25.375" customWidth="1"/>
-    <col min="3" max="3" width="19.75" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="18.125" customWidth="1"/>
-    <col min="6" max="6" width="20.875" customWidth="1"/>
-    <col min="8" max="8" width="14.875" customWidth="1"/>
-    <col min="9" max="9" width="39.75" customWidth="1"/>
-    <col min="13" max="13" width="81.375" customWidth="1"/>
-    <col min="14" max="14" width="41" customWidth="1"/>
-    <col min="15" max="15" width="15.625" customWidth="1"/>
-    <col min="16" max="16" width="29" customWidth="1"/>
-    <col min="17" max="17" width="21.875" customWidth="1"/>
-    <col min="18" max="18" width="33" customWidth="1"/>
-    <col min="24" max="24" width="27.625" customWidth="1"/>
-    <col min="32" max="32" width="20.375" customWidth="1"/>
-    <col min="33" max="33" width="25.5" customWidth="1"/>
-    <col min="34" max="34" width="27" customWidth="1"/>
-    <col min="35" max="35" width="28.375" customWidth="1"/>
+    <col min="2" max="2" width="25.372727" customWidth="1"/>
+    <col min="3" max="3" width="19.745455" customWidth="1"/>
+    <col min="4" max="4" width="15.000000" customWidth="1"/>
+    <col min="5" max="5" width="18.127273" customWidth="1"/>
+    <col min="6" max="6" width="20.872727" customWidth="1"/>
+    <col min="8" max="8" width="14.872727" customWidth="1"/>
+    <col min="9" max="9" width="39.745455" customWidth="1"/>
+    <col min="13" max="13" width="81.372727" customWidth="1"/>
+    <col min="14" max="14" width="41.000000" customWidth="1"/>
+    <col min="15" max="15" width="15.627273" customWidth="1"/>
+    <col min="16" max="16" width="29.000000" customWidth="1"/>
+    <col min="17" max="17" width="21.872727" customWidth="1"/>
+    <col min="18" max="18" width="33.000000" customWidth="1"/>
+    <col min="24" max="24" width="27.627273" customWidth="1"/>
+    <col min="32" max="32" width="20.372727" customWidth="1"/>
+    <col min="33" max="33" width="25.500000" customWidth="1"/>
+    <col min="34" max="34" width="27.000000" customWidth="1"/>
+    <col min="35" max="35" width="28.372727" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36">
+    <row r="1" spans="1:35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2377,20 +3623,20 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" ht="66" customHeight="1" spans="1:36">
-      <c r="B2" s="4" t="s">
+    <row r="2" spans="2:36" ht="66" customHeight="1">
+      <c r="B2" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="52" t="s">
         <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="52" t="s">
         <v>39</v>
       </c>
       <c r="G2" t="s">
@@ -2402,22 +3648,22 @@
       <c r="J2" t="s">
         <v>42</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="52" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="52" t="s">
         <v>48</v>
       </c>
       <c r="Q2" t="s">
@@ -2426,7 +3672,7 @@
       <c r="R2" t="s">
         <v>50</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="S2" s="52" t="s">
         <v>51</v>
       </c>
       <c r="T2" t="s">
@@ -2438,22 +3684,22 @@
       <c r="V2" t="s">
         <v>52</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="W2" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="X2" s="52" t="s">
         <v>54</v>
       </c>
-      <c r="Y2" s="4" t="s">
+      <c r="Y2" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="Z2" s="4" t="s">
+      <c r="Z2" s="52" t="s">
         <v>56</v>
       </c>
-      <c r="AA2" s="4" t="s">
+      <c r="AA2" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="AB2" s="4" t="s">
+      <c r="AB2" s="52" t="s">
         <v>58</v>
       </c>
       <c r="AC2" t="s">
@@ -2468,18 +3714,18 @@
       <c r="AF2" t="s">
         <v>62</v>
       </c>
-      <c r="AG2" s="4" t="s">
+      <c r="AG2" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="AH2" s="4" t="s">
+      <c r="AH2" s="52" t="s">
         <v>64</v>
       </c>
       <c r="AI2" t="s">
         <v>65</v>
       </c>
-      <c r="AJ2" s="5"/>
-    </row>
-    <row r="3" ht="14.25" spans="1:36">
+      <c r="AJ2" s="53"/>
+    </row>
+    <row r="3" spans="1:36">
       <c r="A3" t="s">
         <v>66</v>
       </c>
@@ -2585,9 +3831,9 @@
       <c r="AI3" t="s">
         <v>68</v>
       </c>
-      <c r="AJ3" s="5"/>
-    </row>
-    <row r="4" ht="14.25" spans="1:36">
+      <c r="AJ3" s="53"/>
+    </row>
+    <row r="4" spans="1:36">
       <c r="A4" t="s">
         <v>71</v>
       </c>
@@ -2693,16 +3939,16 @@
       <c r="AI4" t="s">
         <v>105</v>
       </c>
-      <c r="AJ4" s="5"/>
-    </row>
-    <row r="5" ht="14.25" spans="1:36">
-      <c r="A5">
+      <c r="AJ4" s="53"/>
+    </row>
+    <row r="5" spans="1:36">
+      <c r="A5" t="n">
         <v>10001</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="s">
@@ -2714,45 +3960,42 @@
       <c r="AG5" t="s">
         <v>108</v>
       </c>
-      <c r="AH5">
+      <c r="AH5" t="n">
         <v>1254003899</v>
       </c>
-      <c r="AI5" t="s">
+      <c r="AJ5" s="53"/>
+    </row>
+    <row r="6" spans="1:35">
+      <c r="A6" t="n">
+        <v>10002</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
         <v>109</v>
       </c>
-      <c r="AJ5" s="5"/>
-    </row>
-    <row r="6" spans="1:36">
-      <c r="A6">
-        <v>10002</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="I6" t="s">
         <v>110</v>
       </c>
-      <c r="I6" t="s">
+      <c r="AI6" t="s">
         <v>111</v>
       </c>
-      <c r="AI6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36">
-      <c r="A7">
+    </row>
+    <row r="7" spans="1:35">
+      <c r="A7" t="n">
         <v>10003</v>
       </c>
       <c r="B7" t="s">
         <v>112</v>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
         <v>3</v>
       </c>
       <c r="E7" t="s">
@@ -2764,50 +4007,48 @@
       <c r="I7" t="s">
         <v>115</v>
       </c>
-      <c r="J7">
-        <v>1000</v>
-      </c>
-      <c r="K7">
+      <c r="J7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="M7" t="s">
         <v>116</v>
       </c>
-      <c r="S7">
+      <c r="S7" t="n">
         <v>2</v>
       </c>
-      <c r="T7">
+      <c r="T7" t="n">
         <v>5000</v>
       </c>
-      <c r="U7">
+      <c r="U7" t="n">
         <v>5000</v>
       </c>
-      <c r="V7">
+      <c r="V7" t="n">
         <v>5000</v>
       </c>
-      <c r="AC7">
+      <c r="AC7" t="n">
         <v>100404</v>
       </c>
       <c r="AF7" t="s">
         <v>117</v>
       </c>
-      <c r="AG7"/>
-      <c r="AH7"/>
       <c r="AI7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="8" spans="1:36">
-      <c r="A8">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35">
+      <c r="A8" t="n">
         <v>10004</v>
       </c>
       <c r="B8" t="s">
         <v>118</v>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="s">
@@ -2819,50 +4060,48 @@
       <c r="I8" t="s">
         <v>115</v>
       </c>
-      <c r="J8">
-        <v>1000</v>
-      </c>
-      <c r="K8">
+      <c r="J8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="M8" t="s">
         <v>120</v>
       </c>
-      <c r="S8">
+      <c r="S8" t="n">
         <v>2</v>
       </c>
-      <c r="T8">
+      <c r="T8" t="n">
         <v>5000</v>
       </c>
-      <c r="U8">
+      <c r="U8" t="n">
         <v>5000</v>
       </c>
-      <c r="V8">
+      <c r="V8" t="n">
         <v>5000</v>
       </c>
-      <c r="AC8">
+      <c r="AC8" t="n">
         <v>100404</v>
       </c>
       <c r="AF8" t="s">
         <v>121</v>
       </c>
-      <c r="AG8"/>
-      <c r="AH8"/>
       <c r="AI8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36">
-      <c r="A9">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35">
+      <c r="A9" t="n">
         <v>10005</v>
       </c>
       <c r="B9" t="s">
         <v>122</v>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
         <v>3</v>
       </c>
       <c r="E9" t="s">
@@ -2874,50 +4113,48 @@
       <c r="I9" t="s">
         <v>115</v>
       </c>
-      <c r="J9">
-        <v>1000</v>
-      </c>
-      <c r="K9">
+      <c r="J9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="M9" t="s">
         <v>124</v>
       </c>
-      <c r="S9">
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="T9">
+      <c r="T9" t="n">
         <v>5000</v>
       </c>
-      <c r="U9">
+      <c r="U9" t="n">
         <v>5000</v>
       </c>
-      <c r="V9">
+      <c r="V9" t="n">
         <v>5000</v>
       </c>
-      <c r="AC9">
+      <c r="AC9" t="n">
         <v>100404</v>
       </c>
       <c r="AF9" t="s">
         <v>125</v>
       </c>
-      <c r="AG9"/>
-      <c r="AH9"/>
       <c r="AI9" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="10" spans="1:36">
-      <c r="A10">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35">
+      <c r="A10" t="n">
         <v>10006</v>
       </c>
       <c r="B10" t="s">
         <v>126</v>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
         <v>3</v>
       </c>
       <c r="E10" t="s">
@@ -2929,50 +4166,48 @@
       <c r="I10" t="s">
         <v>115</v>
       </c>
-      <c r="J10">
-        <v>1000</v>
-      </c>
-      <c r="K10">
+      <c r="J10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="s">
         <v>128</v>
       </c>
-      <c r="S10">
+      <c r="S10" t="n">
         <v>2</v>
       </c>
-      <c r="T10">
+      <c r="T10" t="n">
         <v>5000</v>
       </c>
-      <c r="U10">
+      <c r="U10" t="n">
         <v>5000</v>
       </c>
-      <c r="V10">
+      <c r="V10" t="n">
         <v>5000</v>
       </c>
-      <c r="AC10">
+      <c r="AC10" t="n">
         <v>100404</v>
       </c>
       <c r="AF10" t="s">
         <v>129</v>
       </c>
-      <c r="AG10"/>
-      <c r="AH10"/>
       <c r="AI10" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" spans="1:36">
-      <c r="A11">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35">
+      <c r="A11" t="n">
         <v>10007</v>
       </c>
       <c r="B11" t="s">
         <v>130</v>
       </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
         <v>3</v>
       </c>
       <c r="E11" t="s">
@@ -2984,50 +4219,48 @@
       <c r="I11" t="s">
         <v>115</v>
       </c>
-      <c r="J11">
-        <v>1000</v>
-      </c>
-      <c r="K11">
+      <c r="J11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="M11" t="s">
         <v>132</v>
       </c>
-      <c r="S11">
+      <c r="S11" t="n">
         <v>2</v>
       </c>
-      <c r="T11">
+      <c r="T11" t="n">
         <v>5000</v>
       </c>
-      <c r="U11">
+      <c r="U11" t="n">
         <v>5000</v>
       </c>
-      <c r="V11">
+      <c r="V11" t="n">
         <v>5000</v>
       </c>
-      <c r="AC11">
+      <c r="AC11" t="n">
         <v>100404</v>
       </c>
       <c r="AF11" t="s">
         <v>133</v>
       </c>
-      <c r="AG11"/>
-      <c r="AH11"/>
       <c r="AI11" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="12" spans="1:36">
-      <c r="A12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35">
+      <c r="A12" t="n">
         <v>10008</v>
       </c>
       <c r="B12" t="s">
         <v>134</v>
       </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
         <v>3</v>
       </c>
       <c r="E12" t="s">
@@ -3039,50 +4272,48 @@
       <c r="I12" t="s">
         <v>115</v>
       </c>
-      <c r="J12">
-        <v>1000</v>
-      </c>
-      <c r="K12">
+      <c r="J12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="s">
         <v>136</v>
       </c>
-      <c r="S12">
+      <c r="S12" t="n">
         <v>2</v>
       </c>
-      <c r="T12">
+      <c r="T12" t="n">
         <v>5000</v>
       </c>
-      <c r="U12">
+      <c r="U12" t="n">
         <v>5000</v>
       </c>
-      <c r="V12">
+      <c r="V12" t="n">
         <v>5000</v>
       </c>
-      <c r="AC12">
+      <c r="AC12" t="n">
         <v>100404</v>
       </c>
       <c r="AF12" t="s">
         <v>137</v>
       </c>
-      <c r="AG12"/>
-      <c r="AH12"/>
       <c r="AI12" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13" spans="1:36">
-      <c r="A13">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35">
+      <c r="A13" t="n">
         <v>10009</v>
       </c>
       <c r="B13" t="s">
         <v>138</v>
       </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
         <v>3</v>
       </c>
       <c r="E13" t="s">
@@ -3094,50 +4325,48 @@
       <c r="I13" t="s">
         <v>115</v>
       </c>
-      <c r="J13">
-        <v>1000</v>
-      </c>
-      <c r="K13">
+      <c r="J13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="M13" t="s">
         <v>140</v>
       </c>
-      <c r="S13">
+      <c r="S13" t="n">
         <v>2</v>
       </c>
-      <c r="T13">
+      <c r="T13" t="n">
         <v>5000</v>
       </c>
-      <c r="U13">
+      <c r="U13" t="n">
         <v>5000</v>
       </c>
-      <c r="V13">
+      <c r="V13" t="n">
         <v>5000</v>
       </c>
-      <c r="AC13">
+      <c r="AC13" t="n">
         <v>100404</v>
       </c>
       <c r="AF13" t="s">
         <v>141</v>
       </c>
-      <c r="AG13"/>
-      <c r="AH13"/>
       <c r="AI13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="14" spans="1:36">
-      <c r="A14">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35">
+      <c r="A14" t="n">
         <v>10010</v>
       </c>
       <c r="B14" t="s">
         <v>142</v>
       </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
         <v>3</v>
       </c>
       <c r="E14" t="s">
@@ -3149,50 +4378,48 @@
       <c r="I14" t="s">
         <v>115</v>
       </c>
-      <c r="J14">
-        <v>1000</v>
-      </c>
-      <c r="K14">
+      <c r="J14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="M14" t="s">
         <v>144</v>
       </c>
-      <c r="S14">
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="T14">
+      <c r="T14" t="n">
         <v>5000</v>
       </c>
-      <c r="U14">
+      <c r="U14" t="n">
         <v>5000</v>
       </c>
-      <c r="V14">
+      <c r="V14" t="n">
         <v>5000</v>
       </c>
-      <c r="AC14">
+      <c r="AC14" t="n">
         <v>100404</v>
       </c>
       <c r="AF14" t="s">
         <v>145</v>
       </c>
-      <c r="AG14"/>
-      <c r="AH14"/>
       <c r="AI14" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15" spans="1:36">
-      <c r="A15">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35">
+      <c r="A15" t="n">
         <v>10011</v>
       </c>
       <c r="B15" t="s">
         <v>146</v>
       </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
         <v>3</v>
       </c>
       <c r="E15" t="s">
@@ -3204,50 +4431,48 @@
       <c r="I15" t="s">
         <v>115</v>
       </c>
-      <c r="J15">
-        <v>1000</v>
-      </c>
-      <c r="K15">
+      <c r="J15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="M15" t="s">
         <v>148</v>
       </c>
-      <c r="S15">
+      <c r="S15" t="n">
         <v>2</v>
       </c>
-      <c r="T15">
+      <c r="T15" t="n">
         <v>5000</v>
       </c>
-      <c r="U15">
+      <c r="U15" t="n">
         <v>5000</v>
       </c>
-      <c r="V15">
+      <c r="V15" t="n">
         <v>5000</v>
       </c>
-      <c r="AC15">
+      <c r="AC15" t="n">
         <v>100404</v>
       </c>
       <c r="AF15" t="s">
         <v>149</v>
       </c>
-      <c r="AG15"/>
-      <c r="AH15"/>
       <c r="AI15" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" spans="1:36">
-      <c r="A16">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35">
+      <c r="A16" t="n">
         <v>10012</v>
       </c>
       <c r="B16" t="s">
         <v>150</v>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
         <v>3</v>
       </c>
       <c r="E16" t="s">
@@ -3259,50 +4484,48 @@
       <c r="I16" t="s">
         <v>115</v>
       </c>
-      <c r="J16">
-        <v>1000</v>
-      </c>
-      <c r="K16">
+      <c r="J16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="M16" t="s">
         <v>152</v>
       </c>
-      <c r="S16">
+      <c r="S16" t="n">
         <v>2</v>
       </c>
-      <c r="T16">
+      <c r="T16" t="n">
         <v>5000</v>
       </c>
-      <c r="U16">
+      <c r="U16" t="n">
         <v>5000</v>
       </c>
-      <c r="V16">
+      <c r="V16" t="n">
         <v>5000</v>
       </c>
-      <c r="AC16">
+      <c r="AC16" t="n">
         <v>100404</v>
       </c>
       <c r="AF16" t="s">
         <v>133</v>
       </c>
-      <c r="AG16"/>
-      <c r="AH16"/>
       <c r="AI16" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:35">
-      <c r="A17">
+      <c r="A17" t="n">
         <v>10013</v>
       </c>
       <c r="B17" t="s">
         <v>153</v>
       </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
         <v>3</v>
       </c>
       <c r="E17" t="s">
@@ -3314,50 +4537,48 @@
       <c r="I17" t="s">
         <v>115</v>
       </c>
-      <c r="J17">
-        <v>1000</v>
-      </c>
-      <c r="K17">
+      <c r="J17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="M17" t="s">
         <v>155</v>
       </c>
-      <c r="S17">
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T17">
+      <c r="T17" t="n">
         <v>5000</v>
       </c>
-      <c r="U17">
+      <c r="U17" t="n">
         <v>5000</v>
       </c>
-      <c r="V17">
+      <c r="V17" t="n">
         <v>5000</v>
       </c>
-      <c r="AC17">
+      <c r="AC17" t="n">
         <v>100404</v>
       </c>
       <c r="AF17" t="s">
         <v>156</v>
       </c>
-      <c r="AG17"/>
-      <c r="AH17"/>
       <c r="AI17" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:35">
-      <c r="A18">
+      <c r="A18" t="n">
         <v>10014</v>
       </c>
       <c r="B18" t="s">
         <v>157</v>
       </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
         <v>3</v>
       </c>
       <c r="E18" t="s">
@@ -3369,50 +4590,48 @@
       <c r="I18" t="s">
         <v>115</v>
       </c>
-      <c r="J18">
-        <v>1000</v>
-      </c>
-      <c r="K18">
+      <c r="J18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
       </c>
       <c r="M18" t="s">
         <v>159</v>
       </c>
-      <c r="S18">
+      <c r="S18" t="n">
         <v>2</v>
       </c>
-      <c r="T18">
+      <c r="T18" t="n">
         <v>5000</v>
       </c>
-      <c r="U18">
+      <c r="U18" t="n">
         <v>5000</v>
       </c>
-      <c r="V18">
+      <c r="V18" t="n">
         <v>5000</v>
       </c>
-      <c r="AC18">
+      <c r="AC18" t="n">
         <v>100404</v>
       </c>
       <c r="AF18" t="s">
         <v>160</v>
       </c>
-      <c r="AG18"/>
-      <c r="AH18"/>
       <c r="AI18" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:35">
-      <c r="A19">
+      <c r="A19" t="n">
         <v>10015</v>
       </c>
       <c r="B19" t="s">
         <v>161</v>
       </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
         <v>3</v>
       </c>
       <c r="E19" t="s">
@@ -3424,50 +4643,48 @@
       <c r="I19" t="s">
         <v>115</v>
       </c>
-      <c r="J19">
-        <v>1000</v>
-      </c>
-      <c r="K19">
+      <c r="J19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
       </c>
       <c r="M19" t="s">
         <v>163</v>
       </c>
-      <c r="S19">
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T19">
+      <c r="T19" t="n">
         <v>5000</v>
       </c>
-      <c r="U19">
+      <c r="U19" t="n">
         <v>5000</v>
       </c>
-      <c r="V19">
+      <c r="V19" t="n">
         <v>5000</v>
       </c>
-      <c r="AC19">
+      <c r="AC19" t="n">
         <v>100404</v>
       </c>
       <c r="AF19" t="s">
         <v>164</v>
       </c>
-      <c r="AG19"/>
-      <c r="AH19"/>
       <c r="AI19" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:35">
-      <c r="A20">
+      <c r="A20" t="n">
         <v>10016</v>
       </c>
       <c r="B20" t="s">
         <v>165</v>
       </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
         <v>3</v>
       </c>
       <c r="E20" t="s">
@@ -3479,109 +4696,108 @@
       <c r="I20" t="s">
         <v>115</v>
       </c>
-      <c r="J20">
-        <v>1000</v>
-      </c>
-      <c r="K20">
+      <c r="J20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
       </c>
       <c r="M20" t="s">
         <v>167</v>
       </c>
-      <c r="S20">
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="T20">
+      <c r="T20" t="n">
         <v>5000</v>
       </c>
-      <c r="U20">
+      <c r="U20" t="n">
         <v>5000</v>
       </c>
-      <c r="V20">
+      <c r="V20" t="n">
         <v>5000</v>
       </c>
-      <c r="AC20">
+      <c r="AC20" t="n">
         <v>100404</v>
       </c>
       <c r="AF20" t="s">
         <v>168</v>
       </c>
-      <c r="AG20"/>
-      <c r="AH20"/>
       <c r="AI20" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="21" s="3" customFormat="1" spans="1:35">
-      <c r="A21" s="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="1:35" s="51" customFormat="1">
+      <c r="A21" s="51" t="n">
         <v>10017</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="51" t="s">
         <v>169</v>
       </c>
-      <c r="C21" s="3">
-        <v>1</v>
-      </c>
-      <c r="D21" s="3">
+      <c r="C21" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="51" t="s">
         <v>170</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="H21" s="51" t="s">
         <v>170</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="I21" s="51" t="s">
         <v>171</v>
       </c>
-      <c r="J21" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K21" s="3">
-        <v>1</v>
-      </c>
-      <c r="M21" s="3" t="s">
+      <c r="J21" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K21" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="51" t="s">
         <v>172</v>
       </c>
-      <c r="N21" s="3" t="s">
+      <c r="N21" s="51" t="s">
         <v>173</v>
       </c>
       <c r="Q21"/>
-      <c r="S21" s="3">
+      <c r="S21" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="T21" s="3">
-        <v>1000</v>
-      </c>
-      <c r="U21" s="3">
-        <v>1000</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="T21" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U21" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V21" s="51" t="n">
         <v>8000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="51" t="n">
         <v>100404</v>
       </c>
-      <c r="AF21" s="3" t="s">
+      <c r="AF21" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="AG21" s="3"/>
-      <c r="AH21" s="3"/>
-      <c r="AI21" s="3" t="s">
-        <v>109</v>
+      <c r="AH21" t="n">
+        <v>1254003899</v>
+      </c>
+      <c r="AI21" s="51" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:35">
-      <c r="A22">
+      <c r="A22" t="n">
         <v>10018</v>
       </c>
       <c r="B22" t="s">
         <v>175</v>
       </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
         <v>5</v>
       </c>
       <c r="E22" t="s">
@@ -3593,112 +4809,114 @@
       <c r="I22" t="s">
         <v>177</v>
       </c>
-      <c r="J22">
-        <v>1000</v>
-      </c>
-      <c r="K22">
+      <c r="J22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="M22" t="s">
         <v>178</v>
       </c>
-      <c r="N22" s="3" t="s">
+      <c r="N22" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="S22">
+      <c r="S22" t="n">
         <v>2</v>
       </c>
-      <c r="T22" s="3">
-        <v>1000</v>
-      </c>
-      <c r="U22" s="3">
-        <v>1000</v>
-      </c>
-      <c r="V22">
+      <c r="T22" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U22" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V22" t="n">
         <v>5500</v>
       </c>
-      <c r="AC22">
+      <c r="AC22" t="n">
         <v>100404</v>
       </c>
       <c r="AF22" t="s">
         <v>179</v>
       </c>
-      <c r="AG22"/>
-      <c r="AH22"/>
+      <c r="AH22" t="n">
+        <v>1254003899</v>
+      </c>
       <c r="AI22" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="23" s="3" customFormat="1" spans="1:35">
-      <c r="A23" s="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:35" s="51" customFormat="1">
+      <c r="A23" s="51" t="n">
         <v>10019</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="51" t="s">
         <v>180</v>
       </c>
-      <c r="C23" s="3">
-        <v>1</v>
-      </c>
-      <c r="D23" s="3">
+      <c r="C23" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="51" t="s">
         <v>181</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="H23" s="51" t="s">
         <v>181</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="I23" s="51" t="s">
         <v>182</v>
       </c>
-      <c r="J23" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K23" s="3">
-        <v>1</v>
-      </c>
-      <c r="M23" s="3" t="s">
+      <c r="J23" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K23" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="51" t="s">
         <v>183</v>
       </c>
-      <c r="N23" s="3" t="s">
+      <c r="N23" s="51" t="s">
         <v>173</v>
       </c>
       <c r="Q23"/>
-      <c r="S23" s="3">
+      <c r="S23" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="T23" s="3">
-        <v>1000</v>
-      </c>
-      <c r="U23" s="3">
-        <v>1000</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="T23" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U23" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V23" s="51" t="n">
         <v>4500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AC23" s="51" t="n">
         <v>100404</v>
       </c>
-      <c r="AF23" s="3" t="s">
+      <c r="AF23" s="51" t="s">
         <v>184</v>
       </c>
-      <c r="AG23" s="3"/>
-      <c r="AH23" s="3"/>
-      <c r="AI23" s="3" t="s">
-        <v>109</v>
+      <c r="AH23" t="n">
+        <v>1254003899</v>
+      </c>
+      <c r="AI23" s="51" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:35">
-      <c r="A24">
+      <c r="A24" t="n">
         <v>10020</v>
       </c>
       <c r="B24" t="s">
         <v>185</v>
       </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24">
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
         <v>7</v>
       </c>
       <c r="E24" t="s">
@@ -3710,112 +4928,114 @@
       <c r="I24" t="s">
         <v>187</v>
       </c>
-      <c r="J24">
-        <v>1000</v>
-      </c>
-      <c r="K24">
+      <c r="J24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
       </c>
       <c r="M24" t="s">
         <v>188</v>
       </c>
-      <c r="N24" s="3" t="s">
+      <c r="N24" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="S24">
+      <c r="S24" t="n">
         <v>2</v>
       </c>
-      <c r="T24" s="3">
-        <v>1000</v>
-      </c>
-      <c r="U24" s="3">
-        <v>1000</v>
-      </c>
-      <c r="V24">
+      <c r="T24" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U24" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V24" t="n">
         <v>3500</v>
       </c>
-      <c r="AC24">
+      <c r="AC24" t="n">
         <v>100404</v>
       </c>
       <c r="AF24" t="s">
         <v>189</v>
       </c>
-      <c r="AG24"/>
-      <c r="AH24"/>
+      <c r="AH24" t="n">
+        <v>1254003899</v>
+      </c>
       <c r="AI24" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="25" s="3" customFormat="1" spans="1:35">
-      <c r="A25" s="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="25" spans="1:35" s="51" customFormat="1">
+      <c r="A25" s="51" t="n">
         <v>10021</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="51" t="s">
         <v>190</v>
       </c>
-      <c r="C25" s="3">
-        <v>1</v>
-      </c>
-      <c r="D25" s="3">
+      <c r="C25" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="51" t="n">
         <v>8</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="51" t="s">
         <v>191</v>
       </c>
-      <c r="H25" s="3" t="s">
+      <c r="H25" s="51" t="s">
         <v>191</v>
       </c>
-      <c r="I25" s="3" t="s">
+      <c r="I25" s="51" t="s">
         <v>192</v>
       </c>
-      <c r="J25" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K25" s="3">
-        <v>1</v>
-      </c>
-      <c r="M25" s="3" t="s">
+      <c r="J25" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K25" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="51" t="s">
         <v>193</v>
       </c>
-      <c r="N25" s="3" t="s">
+      <c r="N25" s="51" t="s">
         <v>173</v>
       </c>
       <c r="Q25"/>
-      <c r="S25" s="3">
+      <c r="S25" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="3">
-        <v>0</v>
-      </c>
-      <c r="U25" s="3">
-        <v>0</v>
-      </c>
-      <c r="V25" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC25" s="3">
+      <c r="T25" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U25" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V25" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AC25" s="51" t="n">
         <v>100404</v>
       </c>
-      <c r="AF25" s="3" t="s">
+      <c r="AF25" s="51" t="s">
         <v>194</v>
       </c>
-      <c r="AG25" s="3"/>
-      <c r="AH25" s="3"/>
-      <c r="AI25" s="3" t="s">
-        <v>109</v>
+      <c r="AH25" t="n">
+        <v>1254003899</v>
+      </c>
+      <c r="AI25" s="51" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:35">
-      <c r="A26">
+      <c r="A26" t="n">
         <v>10022</v>
       </c>
       <c r="B26" t="s">
         <v>195</v>
       </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26">
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>9</v>
       </c>
       <c r="E26" t="s">
@@ -3827,112 +5047,114 @@
       <c r="I26" t="s">
         <v>197</v>
       </c>
-      <c r="J26">
-        <v>1000</v>
-      </c>
-      <c r="K26">
+      <c r="J26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="M26" t="s">
         <v>198</v>
       </c>
-      <c r="N26" s="3" t="s">
+      <c r="N26" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="S26">
+      <c r="S26" t="n">
         <v>2</v>
       </c>
-      <c r="T26" s="3">
-        <v>1000</v>
-      </c>
-      <c r="U26" s="3">
-        <v>1000</v>
-      </c>
-      <c r="V26">
+      <c r="T26" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U26" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V26" t="n">
         <v>6000</v>
       </c>
-      <c r="AC26">
+      <c r="AC26" t="n">
         <v>100404</v>
       </c>
       <c r="AF26" t="s">
         <v>199</v>
       </c>
-      <c r="AG26"/>
-      <c r="AH26"/>
+      <c r="AH26" t="n">
+        <v>1254003899</v>
+      </c>
       <c r="AI26" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="27" s="3" customFormat="1" spans="1:35">
-      <c r="A27" s="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="27" spans="1:35" s="51" customFormat="1">
+      <c r="A27" s="51" t="n">
         <v>10023</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="51" t="s">
         <v>200</v>
       </c>
-      <c r="C27" s="3">
-        <v>1</v>
-      </c>
-      <c r="D27" s="3">
+      <c r="C27" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="51" t="n">
         <v>10</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="51" t="s">
         <v>201</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="H27" s="51" t="s">
         <v>201</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="I27" s="51" t="s">
         <v>202</v>
       </c>
-      <c r="J27" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K27" s="3">
-        <v>1</v>
-      </c>
-      <c r="M27" s="3" t="s">
+      <c r="J27" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K27" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="51" t="s">
         <v>203</v>
       </c>
-      <c r="N27" s="3" t="s">
+      <c r="N27" s="51" t="s">
         <v>173</v>
       </c>
       <c r="Q27"/>
-      <c r="S27" s="3">
+      <c r="S27" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="3">
+      <c r="T27" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U27" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V27" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AC27" s="51" t="n">
         <v>100404</v>
       </c>
-      <c r="AF27" s="3" t="s">
+      <c r="AF27" s="51" t="s">
         <v>199</v>
       </c>
-      <c r="AG27" s="3"/>
-      <c r="AH27" s="3"/>
-      <c r="AI27" s="3" t="s">
-        <v>109</v>
+      <c r="AH27" t="n">
+        <v>1254003899</v>
+      </c>
+      <c r="AI27" s="51" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:35">
-      <c r="A28">
+      <c r="A28" t="n">
         <v>10024</v>
       </c>
       <c r="B28" t="s">
         <v>204</v>
       </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28">
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
         <v>11</v>
       </c>
       <c r="E28" t="s">
@@ -3944,10 +5166,10 @@
       <c r="I28" t="s">
         <v>206</v>
       </c>
-      <c r="J28">
-        <v>1000</v>
-      </c>
-      <c r="K28">
+      <c r="J28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="M28" t="s">
@@ -3956,100 +5178,102 @@
       <c r="N28" t="s">
         <v>173</v>
       </c>
-      <c r="S28">
+      <c r="S28" t="n">
         <v>2</v>
       </c>
-      <c r="T28" s="3">
-        <v>1000</v>
-      </c>
-      <c r="U28" s="3">
-        <v>1000</v>
-      </c>
-      <c r="V28">
+      <c r="T28" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U28" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V28" t="n">
         <v>3500</v>
       </c>
-      <c r="AC28">
+      <c r="AC28" t="n">
         <v>100404</v>
       </c>
       <c r="AF28" t="s">
         <v>208</v>
       </c>
-      <c r="AG28"/>
-      <c r="AH28"/>
+      <c r="AH28" t="n">
+        <v>1254003899</v>
+      </c>
       <c r="AI28" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="29" s="3" customFormat="1" spans="1:35">
-      <c r="A29" s="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:35" s="51" customFormat="1">
+      <c r="A29" s="51" t="n">
         <v>10025</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="51" t="s">
         <v>209</v>
       </c>
-      <c r="C29" s="3">
-        <v>1</v>
-      </c>
-      <c r="D29" s="3">
+      <c r="C29" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="51" t="n">
         <v>12</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="51" t="s">
         <v>210</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="H29" s="51" t="s">
         <v>210</v>
       </c>
-      <c r="I29" s="3" t="s">
+      <c r="I29" s="51" t="s">
         <v>211</v>
       </c>
-      <c r="J29" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K29" s="3">
-        <v>1</v>
-      </c>
-      <c r="M29" s="3" t="s">
+      <c r="J29" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K29" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" s="51" t="s">
         <v>212</v>
       </c>
-      <c r="N29" s="3" t="s">
+      <c r="N29" s="51" t="s">
         <v>173</v>
       </c>
       <c r="Q29"/>
-      <c r="S29" s="3">
+      <c r="S29" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="T29" s="3">
+      <c r="T29" s="51" t="n">
         <v>500</v>
       </c>
-      <c r="U29" s="3">
+      <c r="U29" s="51" t="n">
         <v>500</v>
       </c>
-      <c r="V29" s="3">
+      <c r="V29" s="51" t="n">
         <v>3500</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="51" t="n">
         <v>100404</v>
       </c>
-      <c r="AF29" s="3" t="s">
+      <c r="AF29" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="AG29" s="3"/>
-      <c r="AH29" s="3"/>
-      <c r="AI29" s="3" t="s">
-        <v>109</v>
+      <c r="AH29" t="n">
+        <v>1254003899</v>
+      </c>
+      <c r="AI29" s="51" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:35">
-      <c r="A30">
+      <c r="A30" t="n">
         <v>10026</v>
       </c>
       <c r="B30" t="s">
         <v>209</v>
       </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
         <v>12</v>
       </c>
       <c r="E30" t="s">
@@ -4061,10 +5285,10 @@
       <c r="I30" t="s">
         <v>211</v>
       </c>
-      <c r="J30">
-        <v>1000</v>
-      </c>
-      <c r="K30">
+      <c r="J30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K30" t="n">
         <v>1</v>
       </c>
       <c r="M30" t="s">
@@ -4073,100 +5297,102 @@
       <c r="N30" t="s">
         <v>173</v>
       </c>
-      <c r="S30">
+      <c r="S30" t="n">
         <v>2</v>
       </c>
-      <c r="T30">
+      <c r="T30" t="n">
         <v>500</v>
       </c>
-      <c r="U30">
+      <c r="U30" t="n">
         <v>500</v>
       </c>
-      <c r="V30">
+      <c r="V30" t="n">
         <v>3500</v>
       </c>
-      <c r="AC30">
+      <c r="AC30" t="n">
         <v>100404</v>
       </c>
       <c r="AF30" t="s">
         <v>208</v>
       </c>
-      <c r="AG30"/>
-      <c r="AH30"/>
+      <c r="AH30" t="n">
+        <v>1254003899</v>
+      </c>
       <c r="AI30" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="31" s="3" customFormat="1" spans="1:35">
-      <c r="A31" s="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="31" spans="1:35" s="51" customFormat="1">
+      <c r="A31" s="51" t="n">
         <v>10027</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="51" t="s">
         <v>214</v>
       </c>
-      <c r="C31" s="3">
-        <v>1</v>
-      </c>
-      <c r="D31" s="3">
+      <c r="C31" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="51" t="n">
         <v>13</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="51" t="s">
         <v>215</v>
       </c>
-      <c r="H31" s="3" t="s">
+      <c r="H31" s="51" t="s">
         <v>215</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="I31" s="51" t="s">
         <v>216</v>
       </c>
-      <c r="J31" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K31" s="3">
-        <v>1</v>
-      </c>
-      <c r="M31" s="3" t="s">
+      <c r="J31" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K31" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="51" t="s">
         <v>217</v>
       </c>
-      <c r="N31" s="3" t="s">
+      <c r="N31" s="51" t="s">
         <v>173</v>
       </c>
       <c r="Q31"/>
-      <c r="S31" s="3">
+      <c r="S31" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="3">
+      <c r="T31" s="51" t="n">
         <v>500</v>
       </c>
-      <c r="U31" s="3">
+      <c r="U31" s="51" t="n">
         <v>500</v>
       </c>
-      <c r="V31" s="3">
+      <c r="V31" s="51" t="n">
         <v>3500</v>
       </c>
-      <c r="AC31" s="3">
+      <c r="AC31" s="51" t="n">
         <v>100404</v>
       </c>
-      <c r="AF31" s="3" t="s">
+      <c r="AF31" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="AG31" s="3"/>
-      <c r="AH31" s="3"/>
-      <c r="AI31" s="3" t="s">
-        <v>109</v>
+      <c r="AH31" t="n">
+        <v>1254003899</v>
+      </c>
+      <c r="AI31" s="51" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:35">
-      <c r="A32">
+      <c r="A32" t="n">
         <v>10028</v>
       </c>
       <c r="B32" t="s">
         <v>218</v>
       </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="D32">
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
         <v>14</v>
       </c>
       <c r="E32" t="s">
@@ -4178,109 +5404,111 @@
       <c r="I32" t="s">
         <v>220</v>
       </c>
-      <c r="J32">
-        <v>1000</v>
-      </c>
-      <c r="K32">
+      <c r="J32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="M32" t="s">
         <v>221</v>
       </c>
-      <c r="N32" s="3" t="s">
+      <c r="N32" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="S32">
+      <c r="S32" t="n">
         <v>2</v>
       </c>
-      <c r="T32">
+      <c r="T32" t="n">
         <v>500</v>
       </c>
-      <c r="U32">
+      <c r="U32" t="n">
         <v>500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="V32" s="51" t="n">
         <v>3500</v>
       </c>
-      <c r="AC32">
+      <c r="AC32" t="n">
         <v>100404</v>
       </c>
       <c r="AF32" t="s">
         <v>199</v>
       </c>
-      <c r="AG32"/>
-      <c r="AH32"/>
+      <c r="AH32" t="n">
+        <v>1254003899</v>
+      </c>
       <c r="AI32" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="33" s="3" customFormat="1" spans="1:35">
-      <c r="A33" s="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="33" spans="1:35" s="51" customFormat="1">
+      <c r="A33" s="51" t="n">
         <v>10029</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="51" t="s">
         <v>222</v>
       </c>
-      <c r="C33" s="3">
-        <v>1</v>
-      </c>
-      <c r="D33" s="3">
+      <c r="C33" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="51" t="n">
         <v>15</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="51" t="s">
         <v>223</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="H33" s="51" t="s">
         <v>223</v>
       </c>
-      <c r="I33" s="3" t="s">
+      <c r="I33" s="51" t="s">
         <v>224</v>
       </c>
-      <c r="J33" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K33" s="3">
-        <v>1</v>
-      </c>
-      <c r="M33" s="3" t="s">
+      <c r="J33" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K33" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="51" t="s">
         <v>225</v>
       </c>
       <c r="Q33"/>
-      <c r="S33" s="3">
+      <c r="S33" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="T33" s="3">
+      <c r="T33" s="51" t="n">
         <v>5000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="U33" s="51" t="n">
         <v>5000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="V33" s="51" t="n">
         <v>5000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AC33" s="51" t="n">
         <v>100404</v>
       </c>
-      <c r="AF33" s="3" t="s">
+      <c r="AF33" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="AG33" s="3"/>
-      <c r="AH33" s="3"/>
-      <c r="AI33" s="3" t="s">
-        <v>109</v>
+      <c r="AH33" t="n">
+        <v>1254003899</v>
+      </c>
+      <c r="AI33" s="51" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:35">
-      <c r="A34">
+      <c r="A34" t="n">
         <v>10030</v>
       </c>
       <c r="B34" t="s">
         <v>226</v>
       </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34">
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
         <v>16</v>
       </c>
       <c r="E34" t="s">
@@ -4292,109 +5520,111 @@
       <c r="I34" t="s">
         <v>228</v>
       </c>
-      <c r="J34">
-        <v>1000</v>
-      </c>
-      <c r="K34">
+      <c r="J34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K34" t="n">
         <v>1</v>
       </c>
       <c r="M34" t="s">
         <v>229</v>
       </c>
-      <c r="S34">
+      <c r="S34" t="n">
         <v>2</v>
       </c>
-      <c r="T34" s="3">
+      <c r="T34" s="51" t="n">
         <v>5000</v>
       </c>
-      <c r="U34" s="3">
+      <c r="U34" s="51" t="n">
         <v>5000</v>
       </c>
-      <c r="V34">
+      <c r="V34" t="n">
         <v>5000</v>
       </c>
-      <c r="AC34">
+      <c r="AC34" s="51" t="n">
         <v>100404</v>
       </c>
       <c r="AF34" t="s">
         <v>174</v>
       </c>
-      <c r="AG34"/>
-      <c r="AH34"/>
+      <c r="AH34" t="n">
+        <v>1254003899</v>
+      </c>
       <c r="AI34" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="35" s="3" customFormat="1" spans="1:35">
-      <c r="A35" s="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="35" spans="1:35" s="51" customFormat="1">
+      <c r="A35" s="51" t="n">
         <v>10031</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="51" t="s">
         <v>230</v>
       </c>
-      <c r="C35" s="3">
-        <v>1</v>
-      </c>
-      <c r="D35" s="3">
+      <c r="C35" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="51" t="n">
         <v>17</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" s="51" t="s">
         <v>231</v>
       </c>
-      <c r="H35" s="3" t="s">
+      <c r="H35" s="51" t="s">
         <v>232</v>
       </c>
-      <c r="I35" s="3" t="s">
+      <c r="I35" s="51" t="s">
         <v>233</v>
       </c>
-      <c r="J35" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K35" s="3">
-        <v>1</v>
-      </c>
-      <c r="M35" s="3" t="s">
+      <c r="J35" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K35" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="51" t="s">
         <v>234</v>
       </c>
-      <c r="N35" s="3" t="s">
+      <c r="N35" s="51" t="s">
         <v>235</v>
       </c>
       <c r="Q35"/>
-      <c r="S35" s="3">
+      <c r="S35" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="T35" s="3">
+      <c r="T35" s="51" t="n">
         <v>500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="U35" s="51" t="n">
         <v>500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="V35" s="51" t="n">
         <v>8000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AC35" s="51" t="n">
         <v>100404</v>
       </c>
-      <c r="AF35" s="3" t="s">
+      <c r="AF35" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="AG35" s="3"/>
-      <c r="AH35" s="3"/>
-      <c r="AI35" s="3" t="s">
-        <v>109</v>
+      <c r="AH35" t="n">
+        <v>1254003899</v>
+      </c>
+      <c r="AI35" s="51" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:35">
-      <c r="A36">
+      <c r="A36" t="n">
         <v>10032</v>
       </c>
       <c r="B36" t="s">
         <v>236</v>
       </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36">
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
         <v>18</v>
       </c>
       <c r="E36" t="s">
@@ -4406,106 +5636,108 @@
       <c r="I36" t="s">
         <v>238</v>
       </c>
-      <c r="J36">
-        <v>1000</v>
-      </c>
-      <c r="K36">
+      <c r="J36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K36" t="n">
         <v>1</v>
       </c>
       <c r="M36" t="s">
         <v>239</v>
       </c>
-      <c r="S36">
+      <c r="S36" t="n">
         <v>2</v>
       </c>
-      <c r="T36">
+      <c r="T36" t="n">
         <v>5000</v>
       </c>
-      <c r="U36">
+      <c r="U36" t="n">
         <v>5000</v>
       </c>
-      <c r="V36">
+      <c r="V36" t="n">
         <v>5000</v>
       </c>
-      <c r="AC36">
-        <v>100404</v>
+      <c r="AC36" t="n">
+        <v>100120</v>
       </c>
       <c r="AF36" t="s">
         <v>174</v>
       </c>
-      <c r="AG36"/>
-      <c r="AH36"/>
+      <c r="AH36" t="n">
+        <v>1254003899</v>
+      </c>
       <c r="AI36" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="37" s="3" customFormat="1" spans="1:35">
-      <c r="A37" s="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="37" spans="1:35" s="51" customFormat="1">
+      <c r="A37" s="51" t="n">
         <v>10033</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="51" t="s">
         <v>240</v>
       </c>
-      <c r="C37" s="3">
-        <v>1</v>
-      </c>
-      <c r="D37" s="3">
+      <c r="C37" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="51" t="n">
         <v>34</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="51" t="s">
         <v>241</v>
       </c>
-      <c r="H37" s="3" t="s">
+      <c r="H37" s="51" t="s">
         <v>241</v>
       </c>
-      <c r="I37" s="3" t="s">
+      <c r="I37" s="51" t="s">
         <v>242</v>
       </c>
-      <c r="J37" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K37" s="3">
-        <v>1</v>
-      </c>
-      <c r="M37" s="3" t="s">
+      <c r="J37" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K37" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" s="51" t="s">
         <v>243</v>
       </c>
       <c r="Q37"/>
-      <c r="S37" s="3">
+      <c r="S37" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="T37">
+      <c r="T37" t="n">
         <v>5000</v>
       </c>
-      <c r="U37">
+      <c r="U37" t="n">
         <v>5000</v>
       </c>
-      <c r="V37" s="3">
+      <c r="V37" s="51" t="n">
         <v>5000</v>
       </c>
-      <c r="AC37" s="3">
-        <v>100404</v>
-      </c>
-      <c r="AF37" s="3" t="s">
+      <c r="AC37" t="n">
+        <v>100120</v>
+      </c>
+      <c r="AF37" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="AG37" s="3"/>
-      <c r="AH37" s="3"/>
-      <c r="AI37" s="3" t="s">
-        <v>109</v>
+      <c r="AH37" t="n">
+        <v>1254003899</v>
+      </c>
+      <c r="AI37" s="51" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:35">
-      <c r="A38">
+      <c r="A38" t="n">
         <v>10034</v>
       </c>
       <c r="B38" t="s">
         <v>244</v>
       </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38">
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
         <v>35</v>
       </c>
       <c r="E38" t="s">
@@ -4517,106 +5749,108 @@
       <c r="I38" t="s">
         <v>246</v>
       </c>
-      <c r="J38">
-        <v>1000</v>
-      </c>
-      <c r="K38">
+      <c r="J38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="M38" t="s">
         <v>247</v>
       </c>
-      <c r="S38">
+      <c r="S38" t="n">
         <v>2</v>
       </c>
-      <c r="T38">
+      <c r="T38" t="n">
         <v>5000</v>
       </c>
-      <c r="U38">
+      <c r="U38" t="n">
         <v>5000</v>
       </c>
-      <c r="V38">
+      <c r="V38" t="n">
         <v>5000</v>
       </c>
-      <c r="AC38">
-        <v>100404</v>
+      <c r="AC38" t="n">
+        <v>100120</v>
       </c>
       <c r="AF38" t="s">
         <v>199</v>
       </c>
-      <c r="AG38"/>
-      <c r="AH38"/>
+      <c r="AH38" t="n">
+        <v>1254003899</v>
+      </c>
       <c r="AI38" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="39" s="3" customFormat="1" spans="1:35">
-      <c r="A39" s="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="39" spans="1:35" s="51" customFormat="1">
+      <c r="A39" s="51" t="n">
         <v>10035</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="51" t="s">
         <v>248</v>
       </c>
-      <c r="C39" s="3">
-        <v>1</v>
-      </c>
-      <c r="D39" s="3">
+      <c r="C39" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="51" t="n">
         <v>19</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" s="51" t="s">
         <v>249</v>
       </c>
-      <c r="H39" s="3" t="s">
+      <c r="H39" s="51" t="s">
         <v>249</v>
       </c>
-      <c r="I39" s="3" t="s">
+      <c r="I39" s="51" t="s">
         <v>250</v>
       </c>
-      <c r="J39" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K39" s="3">
-        <v>1</v>
-      </c>
-      <c r="M39" s="3" t="s">
+      <c r="J39" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K39" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" s="51" t="s">
         <v>251</v>
       </c>
       <c r="Q39"/>
-      <c r="S39" s="3">
+      <c r="S39" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="T39" s="3">
+      <c r="T39" s="51" t="n">
         <v>5000</v>
       </c>
-      <c r="U39" s="3">
+      <c r="U39" s="51" t="n">
         <v>5000</v>
       </c>
-      <c r="V39" s="3">
+      <c r="V39" s="51" t="n">
         <v>5000</v>
       </c>
-      <c r="AC39" s="3">
-        <v>100404</v>
-      </c>
-      <c r="AF39" s="3" t="s">
+      <c r="AC39" t="n">
+        <v>100120</v>
+      </c>
+      <c r="AF39" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="AG39" s="3"/>
-      <c r="AH39" s="3"/>
-      <c r="AI39" s="3" t="s">
-        <v>109</v>
+      <c r="AH39" t="n">
+        <v>1254003899</v>
+      </c>
+      <c r="AI39" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:35">
-      <c r="A40">
+      <c r="A40" t="n">
         <v>10036</v>
       </c>
       <c r="B40" t="s">
         <v>252</v>
       </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40">
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
         <v>20</v>
       </c>
       <c r="E40" t="s">
@@ -4628,106 +5862,108 @@
       <c r="I40" t="s">
         <v>254</v>
       </c>
-      <c r="J40">
-        <v>1000</v>
-      </c>
-      <c r="K40">
+      <c r="J40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K40" t="n">
         <v>1</v>
       </c>
       <c r="M40" t="s">
         <v>255</v>
       </c>
-      <c r="S40">
+      <c r="S40" t="n">
         <v>2</v>
       </c>
-      <c r="T40">
+      <c r="T40" t="n">
         <v>5000</v>
       </c>
-      <c r="U40">
+      <c r="U40" t="n">
         <v>5000</v>
       </c>
-      <c r="V40">
+      <c r="V40" t="n">
         <v>5000</v>
       </c>
-      <c r="AC40">
-        <v>100404</v>
+      <c r="AC40" t="n">
+        <v>100120</v>
       </c>
       <c r="AF40" t="s">
         <v>174</v>
       </c>
-      <c r="AG40"/>
-      <c r="AH40"/>
+      <c r="AH40" t="n">
+        <v>1254003899</v>
+      </c>
       <c r="AI40" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="41" s="3" customFormat="1" spans="1:35">
-      <c r="A41" s="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="41" spans="1:35" s="51" customFormat="1">
+      <c r="A41" s="51" t="n">
         <v>10037</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="51" t="s">
         <v>256</v>
       </c>
-      <c r="C41" s="3">
-        <v>1</v>
-      </c>
-      <c r="D41" s="3">
+      <c r="C41" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="51" t="n">
         <v>20</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="E41" s="51" t="s">
         <v>257</v>
       </c>
-      <c r="H41" s="3" t="s">
+      <c r="H41" s="51" t="s">
         <v>257</v>
       </c>
-      <c r="I41" s="3" t="s">
+      <c r="I41" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="J41" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K41" s="3">
-        <v>1</v>
-      </c>
-      <c r="M41" s="3" t="s">
+      <c r="J41" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K41" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" s="51" t="s">
         <v>255</v>
       </c>
       <c r="Q41"/>
-      <c r="S41" s="3">
+      <c r="S41" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="T41" s="3">
+      <c r="T41" s="51" t="n">
         <v>5000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="U41" s="51" t="n">
         <v>5000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="V41" s="51" t="n">
         <v>5000</v>
       </c>
-      <c r="AC41" s="3">
-        <v>100404</v>
-      </c>
-      <c r="AF41" s="3" t="s">
+      <c r="AC41" t="n">
+        <v>100120</v>
+      </c>
+      <c r="AF41" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="AG41" s="3"/>
-      <c r="AH41" s="3"/>
-      <c r="AI41" s="3" t="s">
-        <v>109</v>
+      <c r="AH41" t="n">
+        <v>1254003899</v>
+      </c>
+      <c r="AI41" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:35">
-      <c r="A42">
+      <c r="A42" t="n">
         <v>10038</v>
       </c>
       <c r="B42" t="s">
         <v>259</v>
       </c>
-      <c r="C42">
-        <v>1</v>
-      </c>
-      <c r="D42">
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
         <v>21</v>
       </c>
       <c r="E42" t="s">
@@ -4739,106 +5975,108 @@
       <c r="I42" t="s">
         <v>261</v>
       </c>
-      <c r="J42">
-        <v>1000</v>
-      </c>
-      <c r="K42">
+      <c r="J42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K42" t="n">
         <v>1</v>
       </c>
       <c r="M42" t="s">
         <v>262</v>
       </c>
-      <c r="S42">
+      <c r="S42" t="n">
         <v>2</v>
       </c>
-      <c r="T42">
+      <c r="T42" t="n">
         <v>3500</v>
       </c>
-      <c r="U42">
+      <c r="U42" t="n">
         <v>3500</v>
       </c>
-      <c r="V42">
+      <c r="V42" t="n">
         <v>3500</v>
       </c>
-      <c r="AC42">
-        <v>100404</v>
+      <c r="AC42" t="n">
+        <v>100120</v>
       </c>
       <c r="AF42" t="s">
         <v>179</v>
       </c>
-      <c r="AG42"/>
-      <c r="AH42"/>
+      <c r="AH42" t="n">
+        <v>1254003899</v>
+      </c>
       <c r="AI42" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="43" s="3" customFormat="1" spans="1:35">
-      <c r="A43" s="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="43" spans="1:35" s="51" customFormat="1">
+      <c r="A43" s="51" t="n">
         <v>10039</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="51" t="s">
         <v>259</v>
       </c>
-      <c r="C43" s="3">
-        <v>1</v>
-      </c>
-      <c r="D43" s="3">
+      <c r="C43" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="51" t="n">
         <v>21</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E43" s="51" t="s">
         <v>260</v>
       </c>
-      <c r="H43" s="3" t="s">
+      <c r="H43" s="51" t="s">
         <v>260</v>
       </c>
-      <c r="I43" s="3" t="s">
+      <c r="I43" s="51" t="s">
         <v>261</v>
       </c>
-      <c r="J43" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K43" s="3">
-        <v>1</v>
-      </c>
-      <c r="M43" s="3" t="s">
+      <c r="J43" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K43" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" s="51" t="s">
         <v>263</v>
       </c>
       <c r="Q43"/>
-      <c r="S43" s="3">
+      <c r="S43" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="T43" s="3">
+      <c r="T43" s="51" t="n">
         <v>3500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="U43" s="51" t="n">
         <v>3500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="V43" s="51" t="n">
         <v>3500</v>
       </c>
-      <c r="AC43" s="3">
-        <v>100404</v>
-      </c>
-      <c r="AF43" s="3" t="s">
+      <c r="AC43" t="n">
+        <v>100120</v>
+      </c>
+      <c r="AF43" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="AG43" s="3"/>
-      <c r="AH43" s="3"/>
-      <c r="AI43" s="3" t="s">
-        <v>109</v>
+      <c r="AH43" t="n">
+        <v>1254003899</v>
+      </c>
+      <c r="AI43" s="51" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="1:35">
-      <c r="A44">
+      <c r="A44" t="n">
         <v>10040</v>
       </c>
       <c r="B44" t="s">
         <v>264</v>
       </c>
-      <c r="C44">
-        <v>1</v>
-      </c>
-      <c r="D44">
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
         <v>23</v>
       </c>
       <c r="E44" t="s">
@@ -4850,1016 +6088,1283 @@
       <c r="I44" t="s">
         <v>266</v>
       </c>
-      <c r="J44">
-        <v>1000</v>
-      </c>
-      <c r="K44">
+      <c r="J44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="M44" t="s">
         <v>267</v>
       </c>
-      <c r="S44">
+      <c r="S44" t="n">
         <v>2</v>
       </c>
-      <c r="T44" s="3">
+      <c r="T44" s="51" t="n">
         <v>3500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="U44" s="51" t="n">
         <v>3500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="V44" s="51" t="n">
         <v>3500</v>
       </c>
-      <c r="AC44">
-        <v>100404</v>
+      <c r="AC44" t="n">
+        <v>100120</v>
       </c>
       <c r="AF44" t="s">
         <v>179</v>
       </c>
-      <c r="AG44"/>
-      <c r="AH44"/>
+      <c r="AH44" t="n">
+        <v>1254003899</v>
+      </c>
       <c r="AI44" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="45" s="3" customFormat="1" spans="1:35">
-      <c r="A45" s="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45" spans="1:35" s="51" customFormat="1">
+      <c r="A45" s="51" t="n">
         <v>10041</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="51" t="s">
         <v>268</v>
       </c>
-      <c r="C45" s="3">
-        <v>1</v>
-      </c>
-      <c r="D45" s="3">
+      <c r="C45" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="51" t="n">
         <v>24</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="E45" s="51" t="s">
         <v>269</v>
       </c>
-      <c r="H45" s="3" t="s">
+      <c r="H45" s="51" t="s">
         <v>269</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="I45" s="51" t="s">
         <v>270</v>
       </c>
-      <c r="J45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K45" s="3">
-        <v>1</v>
-      </c>
-      <c r="M45" s="3" t="s">
+      <c r="J45" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K45" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" s="51" t="s">
         <v>271</v>
       </c>
       <c r="Q45"/>
-      <c r="S45" s="3">
+      <c r="S45" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="T45" s="3">
+      <c r="T45" s="51" t="n">
         <v>3500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="U45" s="51" t="n">
         <v>3500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="V45" s="51" t="n">
         <v>3500</v>
       </c>
-      <c r="AC45" s="3">
-        <v>100404</v>
-      </c>
-      <c r="AF45" s="3" t="s">
+      <c r="AC45" t="n">
+        <v>100120</v>
+      </c>
+      <c r="AF45" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="AG45" s="3"/>
-      <c r="AH45" s="3"/>
-      <c r="AI45" s="3" t="s">
-        <v>109</v>
+      <c r="AH45" t="n">
+        <v>1254003899</v>
+      </c>
+      <c r="AI45" s="51" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:35">
-      <c r="A46">
+      <c r="A46" t="n">
         <v>10042</v>
       </c>
       <c r="B46" t="s">
-        <v>268</v>
-      </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-      <c r="D46">
+        <v>272</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
         <v>25</v>
       </c>
       <c r="E46" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H46" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I46" t="s">
-        <v>273</v>
-      </c>
-      <c r="J46">
-        <v>1000</v>
-      </c>
-      <c r="K46">
+        <v>274</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K46" t="n">
         <v>1</v>
       </c>
       <c r="M46" t="s">
-        <v>274</v>
-      </c>
-      <c r="N46" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="N46" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="S46">
+      <c r="S46" t="n">
         <v>2</v>
       </c>
-      <c r="T46" s="3">
-        <v>1000</v>
-      </c>
-      <c r="U46" s="3">
-        <v>1000</v>
-      </c>
-      <c r="V46">
+      <c r="T46" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U46" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V46" t="n">
         <v>5500</v>
       </c>
-      <c r="AC46">
+      <c r="AC46" t="n">
         <v>100404</v>
       </c>
       <c r="AF46" t="s">
         <v>179</v>
       </c>
-      <c r="AG46"/>
-      <c r="AH46"/>
+      <c r="AH46" t="n">
+        <v>1254003899</v>
+      </c>
       <c r="AI46" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="47" s="3" customFormat="1" spans="1:35">
-      <c r="A47" s="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="47" spans="1:35" s="51" customFormat="1">
+      <c r="A47" s="51" t="n">
         <v>10043</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C47" s="3">
-        <v>1</v>
-      </c>
-      <c r="D47" s="3">
+      <c r="B47" s="51" t="s">
+        <v>276</v>
+      </c>
+      <c r="C47" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="51" t="n">
         <v>26</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E47" s="51" t="s">
+        <v>277</v>
+      </c>
+      <c r="H47" s="51" t="s">
+        <v>277</v>
+      </c>
+      <c r="I47" s="51" t="s">
+        <v>278</v>
+      </c>
+      <c r="J47" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K47" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" s="51" t="s">
+        <v>279</v>
+      </c>
+      <c r="N47" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q47"/>
+      <c r="S47" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="T47" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U47" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V47" s="51" t="n">
+        <v>4500</v>
+      </c>
+      <c r="AC47" s="51" t="n">
+        <v>100404</v>
+      </c>
+      <c r="AF47" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1254003899</v>
+      </c>
+      <c r="AI47" s="51" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="48" spans="1:35">
+      <c r="A48" t="n">
+        <v>10044</v>
+      </c>
+      <c r="B48" t="s">
         <v>276</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="I47" s="3" t="s">
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>26</v>
+      </c>
+      <c r="E48" t="s">
         <v>277</v>
       </c>
-      <c r="J47" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K47" s="3">
-        <v>1</v>
-      </c>
-      <c r="M47" s="3" t="s">
+      <c r="H48" t="s">
+        <v>277</v>
+      </c>
+      <c r="I48" t="s">
         <v>278</v>
       </c>
-      <c r="N47" s="3" t="s">
+      <c r="J48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" s="51" t="s">
+        <v>280</v>
+      </c>
+      <c r="N48" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="Q47"/>
-      <c r="S47" s="3">
+      <c r="S48" t="n">
         <v>2</v>
       </c>
-      <c r="T47" s="3">
-        <v>1000</v>
-      </c>
-      <c r="U47" s="3">
-        <v>1000</v>
-      </c>
-      <c r="V47" s="3">
+      <c r="T48" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U48" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V48" s="51" t="n">
         <v>4500</v>
       </c>
-      <c r="AC47" s="3">
-        <v>100404</v>
-      </c>
-      <c r="AF47" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="AG47" s="3"/>
-      <c r="AH47" s="3"/>
-      <c r="AI47" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="48" spans="1:35">
-      <c r="A48">
-        <v>10044</v>
-      </c>
-      <c r="B48" t="s">
-        <v>275</v>
-      </c>
-      <c r="C48">
-        <v>1</v>
-      </c>
-      <c r="D48">
-        <v>26</v>
-      </c>
-      <c r="E48" t="s">
-        <v>276</v>
-      </c>
-      <c r="H48" t="s">
-        <v>276</v>
-      </c>
-      <c r="I48" t="s">
-        <v>277</v>
-      </c>
-      <c r="J48">
-        <v>1000</v>
-      </c>
-      <c r="K48">
-        <v>1</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="S48">
-        <v>2</v>
-      </c>
-      <c r="T48" s="3">
-        <v>1000</v>
-      </c>
-      <c r="U48" s="3">
-        <v>1000</v>
-      </c>
-      <c r="V48" s="3">
-        <v>4500</v>
-      </c>
-      <c r="AC48">
+      <c r="AC48" t="n">
         <v>100404</v>
       </c>
       <c r="AF48" t="s">
         <v>199</v>
       </c>
-      <c r="AG48"/>
-      <c r="AH48"/>
+      <c r="AH48" t="n">
+        <v>1254003899</v>
+      </c>
       <c r="AI48" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="49" s="3" customFormat="1" spans="1:35">
-      <c r="A49" s="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="49" spans="1:35" s="51" customFormat="1">
+      <c r="A49" s="51" t="n">
         <v>10045</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="C49" s="3">
-        <v>1</v>
-      </c>
-      <c r="D49" s="3">
+      <c r="B49" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="C49" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="51" t="n">
         <v>27</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="I49" s="3" t="s">
+      <c r="E49" s="51" t="s">
         <v>282</v>
       </c>
-      <c r="J49" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K49" s="3">
-        <v>1</v>
-      </c>
-      <c r="M49" s="3" t="s">
+      <c r="H49" s="51" t="s">
+        <v>282</v>
+      </c>
+      <c r="I49" s="51" t="s">
         <v>283</v>
       </c>
-      <c r="N49" s="3" t="s">
+      <c r="J49" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K49" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" s="51" t="s">
+        <v>284</v>
+      </c>
+      <c r="N49" s="51" t="s">
         <v>173</v>
       </c>
       <c r="Q49"/>
-      <c r="S49" s="3">
+      <c r="S49" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="T49" s="3">
-        <v>1000</v>
-      </c>
-      <c r="U49" s="3">
-        <v>1000</v>
-      </c>
-      <c r="V49">
+      <c r="T49" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U49" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V49" t="n">
         <v>3500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AC49" s="51" t="n">
         <v>100404</v>
       </c>
-      <c r="AF49" s="3" t="s">
+      <c r="AF49" s="51" t="s">
         <v>194</v>
       </c>
-      <c r="AG49" s="3"/>
-      <c r="AH49" s="3"/>
-      <c r="AI49" s="3" t="s">
-        <v>109</v>
+      <c r="AH49" t="n">
+        <v>1254003899</v>
+      </c>
+      <c r="AI49" s="51" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="50" spans="1:35">
-      <c r="A50">
+      <c r="A50" t="n">
         <v>10046</v>
       </c>
       <c r="B50" t="s">
-        <v>284</v>
-      </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
-      <c r="D50">
+        <v>285</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
         <v>28</v>
       </c>
       <c r="E50" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H50" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I50" t="s">
-        <v>286</v>
-      </c>
-      <c r="J50">
-        <v>1000</v>
-      </c>
-      <c r="K50">
+        <v>287</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K50" t="n">
         <v>1</v>
       </c>
       <c r="M50" t="s">
-        <v>287</v>
-      </c>
-      <c r="N50" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="N50" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="S50">
+      <c r="S50" t="n">
         <v>2</v>
       </c>
-      <c r="T50" s="3">
-        <v>0</v>
-      </c>
-      <c r="U50" s="3">
-        <v>0</v>
-      </c>
-      <c r="V50" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC50">
+      <c r="T50" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U50" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V50" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AC50" t="n">
         <v>100404</v>
       </c>
       <c r="AF50" t="s">
         <v>208</v>
       </c>
-      <c r="AG50"/>
-      <c r="AH50"/>
+      <c r="AH50" t="n">
+        <v>1254003899</v>
+      </c>
       <c r="AI50" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="51" s="3" customFormat="1" spans="1:35">
-      <c r="A51" s="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="51" spans="1:35" s="51" customFormat="1">
+      <c r="A51" s="51" t="n">
         <v>10047</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="C51" s="3">
-        <v>1</v>
-      </c>
-      <c r="D51" s="3">
+      <c r="B51" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="C51" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="51" t="n">
         <v>28</v>
       </c>
-      <c r="E51" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="I51" s="3" t="s">
+      <c r="E51" s="51" t="s">
         <v>286</v>
       </c>
-      <c r="J51" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K51" s="3">
-        <v>1</v>
-      </c>
-      <c r="M51" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="N51" s="3" t="s">
+      <c r="H51" s="51" t="s">
+        <v>286</v>
+      </c>
+      <c r="I51" s="51" t="s">
+        <v>287</v>
+      </c>
+      <c r="J51" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K51" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" s="51" t="s">
+        <v>289</v>
+      </c>
+      <c r="N51" s="51" t="s">
         <v>173</v>
       </c>
       <c r="Q51"/>
-      <c r="S51" s="3">
+      <c r="S51" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="T51" s="3">
-        <v>0</v>
-      </c>
-      <c r="U51" s="3">
-        <v>0</v>
-      </c>
-      <c r="V51" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC51" s="3">
+      <c r="T51" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U51" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V51" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AC51" s="51" t="n">
         <v>100404</v>
       </c>
-      <c r="AF51" s="3" t="s">
+      <c r="AF51" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="AG51" s="3"/>
-      <c r="AH51" s="3"/>
-      <c r="AI51" s="3" t="s">
-        <v>109</v>
+      <c r="AH51" t="n">
+        <v>1254003899</v>
+      </c>
+      <c r="AI51" s="51" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="1:35">
-      <c r="A52">
+      <c r="A52" t="n">
         <v>10048</v>
       </c>
       <c r="B52" t="s">
-        <v>289</v>
-      </c>
-      <c r="C52">
-        <v>1</v>
-      </c>
-      <c r="D52">
+        <v>290</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
         <v>29</v>
       </c>
       <c r="E52" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H52" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I52" t="s">
-        <v>291</v>
-      </c>
-      <c r="J52">
-        <v>1000</v>
-      </c>
-      <c r="K52">
+        <v>292</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K52" t="n">
         <v>1</v>
       </c>
       <c r="M52" t="s">
-        <v>292</v>
-      </c>
-      <c r="S52">
+        <v>293</v>
+      </c>
+      <c r="S52" t="n">
         <v>2</v>
       </c>
-      <c r="T52">
+      <c r="T52" t="n">
         <v>10000</v>
       </c>
-      <c r="U52">
+      <c r="U52" t="n">
         <v>10000</v>
       </c>
-      <c r="V52">
+      <c r="V52" t="n">
         <v>10000</v>
       </c>
-      <c r="AC52">
-        <v>100903</v>
+      <c r="AC52" s="51" t="n">
+        <v>100404</v>
       </c>
       <c r="AF52" t="s">
         <v>174</v>
       </c>
-      <c r="AG52"/>
-      <c r="AH52"/>
+      <c r="AH52" t="n">
+        <v>1254003899</v>
+      </c>
       <c r="AI52" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="53" s="3" customFormat="1" spans="1:35">
-      <c r="A53" s="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="53" spans="1:35" s="51" customFormat="1">
+      <c r="A53" s="51" t="n">
         <v>10049</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="C53" s="3">
-        <v>1</v>
-      </c>
-      <c r="D53" s="3">
+      <c r="B53" s="51" t="s">
+        <v>294</v>
+      </c>
+      <c r="C53" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="51" t="n">
         <v>30</v>
       </c>
-      <c r="E53" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="H53" s="3" t="s">
+      <c r="E53" s="51" t="s">
         <v>295</v>
       </c>
-      <c r="I53" s="3" t="s">
+      <c r="H53" s="51" t="s">
         <v>296</v>
       </c>
-      <c r="J53" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K53" s="3">
-        <v>1</v>
-      </c>
-      <c r="M53" s="3" t="s">
+      <c r="I53" s="51" t="s">
         <v>297</v>
       </c>
-      <c r="N53" s="3" t="s">
+      <c r="J53" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K53" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" s="51" t="s">
+        <v>298</v>
+      </c>
+      <c r="N53" s="51" t="s">
         <v>173</v>
       </c>
       <c r="Q53"/>
-      <c r="S53" s="3">
+      <c r="S53" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="T53" s="3">
+      <c r="T53" s="51" t="n">
         <v>500</v>
       </c>
-      <c r="U53" s="3">
+      <c r="U53" s="51" t="n">
         <v>500</v>
       </c>
-      <c r="V53" s="3">
+      <c r="V53" s="51" t="n">
         <v>5000</v>
       </c>
-      <c r="AF53" s="3" t="s">
+      <c r="AC53" t="n">
+        <v>100120</v>
+      </c>
+      <c r="AF53" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="AG53" s="3"/>
-      <c r="AH53" s="3"/>
-      <c r="AI53" s="3" t="s">
-        <v>109</v>
+      <c r="AG53" s="51" t="s">
+        <v>108</v>
+      </c>
+      <c r="AH53" s="51" t="n">
+        <v>1254003899</v>
+      </c>
+      <c r="AI53" s="51" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:35">
-      <c r="A54">
+      <c r="A54" t="n">
         <v>10050</v>
       </c>
       <c r="B54" t="s">
-        <v>298</v>
-      </c>
-      <c r="C54">
-        <v>1</v>
-      </c>
-      <c r="D54">
+        <v>299</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
         <v>30</v>
       </c>
       <c r="E54" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H54" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I54" t="s">
-        <v>296</v>
-      </c>
-      <c r="J54">
-        <v>1000</v>
-      </c>
-      <c r="K54">
+        <v>297</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K54" t="n">
         <v>1</v>
       </c>
       <c r="M54" t="s">
-        <v>300</v>
-      </c>
-      <c r="N54" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="N54" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="S54">
+      <c r="S54" t="n">
         <v>2</v>
       </c>
-      <c r="T54">
+      <c r="T54" t="n">
         <v>500</v>
       </c>
-      <c r="U54">
+      <c r="U54" t="n">
         <v>500</v>
       </c>
-      <c r="V54">
+      <c r="V54" t="n">
         <v>5000</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>100120</v>
       </c>
       <c r="AF54" t="s">
         <v>174</v>
       </c>
-      <c r="AG54"/>
-      <c r="AH54"/>
+      <c r="AH54" t="n">
+        <v>1254003899</v>
+      </c>
       <c r="AI54" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="55" s="3" customFormat="1" spans="1:35">
-      <c r="A55" s="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="55" spans="1:35" s="51" customFormat="1">
+      <c r="A55" s="51" t="n">
         <v>10051</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="C55" s="3">
-        <v>1</v>
-      </c>
-      <c r="D55" s="3">
+      <c r="B55" s="51" t="s">
+        <v>302</v>
+      </c>
+      <c r="C55" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="51" t="n">
         <v>31</v>
       </c>
-      <c r="E55" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="H55" s="3" t="s">
+      <c r="E55" s="51" t="s">
         <v>303</v>
       </c>
-      <c r="I55" s="3" t="s">
+      <c r="H55" s="51" t="s">
         <v>304</v>
       </c>
-      <c r="J55" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K55" s="3">
-        <v>1</v>
-      </c>
-      <c r="M55" s="3" t="s">
+      <c r="I55" s="51" t="s">
         <v>305</v>
       </c>
-      <c r="N55" s="3" t="s">
+      <c r="J55" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K55" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" s="51" t="s">
+        <v>306</v>
+      </c>
+      <c r="N55" s="51" t="s">
         <v>173</v>
       </c>
       <c r="Q55"/>
-      <c r="S55" s="3">
+      <c r="S55" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="T55" s="3">
+      <c r="T55" s="51" t="n">
         <v>500</v>
       </c>
-      <c r="U55" s="3">
+      <c r="U55" s="51" t="n">
         <v>500</v>
       </c>
-      <c r="V55" s="3">
+      <c r="V55" s="51" t="n">
         <v>4000</v>
       </c>
-      <c r="AF55" s="3" t="s">
+      <c r="AC55" t="n">
+        <v>100120</v>
+      </c>
+      <c r="AF55" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="AG55" s="3"/>
-      <c r="AH55" s="3"/>
-      <c r="AI55" s="3" t="s">
-        <v>109</v>
+      <c r="AH55" t="n">
+        <v>1254003899</v>
+      </c>
+      <c r="AI55" s="51" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="56" spans="1:35">
-      <c r="A56">
+      <c r="A56" t="n">
         <v>10052</v>
       </c>
       <c r="B56" t="s">
-        <v>306</v>
-      </c>
-      <c r="C56">
-        <v>1</v>
-      </c>
-      <c r="D56">
+        <v>307</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="n">
         <v>31</v>
       </c>
       <c r="E56" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H56" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I56" t="s">
-        <v>304</v>
-      </c>
-      <c r="J56">
-        <v>1000</v>
-      </c>
-      <c r="K56">
+        <v>305</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K56" t="n">
         <v>1</v>
       </c>
       <c r="M56" t="s">
-        <v>308</v>
-      </c>
-      <c r="N56" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="N56" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="S56">
+      <c r="S56" t="n">
         <v>2</v>
       </c>
-      <c r="T56">
+      <c r="T56" t="n">
         <v>500</v>
       </c>
-      <c r="U56">
+      <c r="U56" t="n">
         <v>500</v>
       </c>
-      <c r="V56">
+      <c r="V56" t="n">
         <v>4000</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>100120</v>
       </c>
       <c r="AF56" t="s">
         <v>174</v>
       </c>
-      <c r="AG56"/>
-      <c r="AH56"/>
+      <c r="AH56" t="n">
+        <v>1254003899</v>
+      </c>
       <c r="AI56" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="57" s="3" customFormat="1" spans="1:35">
-      <c r="A57" s="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="57" spans="1:35" s="51" customFormat="1">
+      <c r="A57" s="51" t="n">
         <v>10053</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C57" s="3">
-        <v>1</v>
-      </c>
-      <c r="D57" s="3">
+      <c r="B57" s="51" t="s">
+        <v>310</v>
+      </c>
+      <c r="C57" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="51" t="n">
         <v>32</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="H57" s="3" t="s">
+      <c r="E57" s="51" t="s">
         <v>311</v>
       </c>
-      <c r="I57" s="3" t="s">
+      <c r="H57" s="51" t="s">
         <v>312</v>
       </c>
-      <c r="J57" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K57" s="3">
-        <v>1</v>
-      </c>
-      <c r="M57" s="3" t="s">
+      <c r="I57" s="51" t="s">
         <v>313</v>
       </c>
-      <c r="N57" s="3" t="s">
+      <c r="J57" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K57" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" s="51" t="s">
+        <v>314</v>
+      </c>
+      <c r="S57" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="T57" s="51" t="n">
+        <v>9000</v>
+      </c>
+      <c r="U57" s="51" t="n">
+        <v>9000</v>
+      </c>
+      <c r="V57" s="51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>100120</v>
+      </c>
+      <c r="AF57" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1254003899</v>
+      </c>
+      <c r="AI57" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="1:35">
+      <c r="A58" t="n">
+        <v>10054</v>
+      </c>
+      <c r="B58" t="s">
+        <v>315</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>33</v>
+      </c>
+      <c r="E58" t="s">
+        <v>316</v>
+      </c>
+      <c r="H58" t="s">
+        <v>317</v>
+      </c>
+      <c r="I58" t="s">
+        <v>318</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" t="s">
+        <v>319</v>
+      </c>
+      <c r="N58" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="S57" s="3">
+      <c r="S58" t="n">
         <v>2</v>
       </c>
-      <c r="T57" s="3">
+      <c r="T58" t="n">
         <v>500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="U58" t="n">
         <v>500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="V58" t="n">
         <v>3000</v>
       </c>
-      <c r="AC57" s="3">
-        <v>100120</v>
-      </c>
-      <c r="AF57" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="AG57" s="3"/>
-      <c r="AH57" s="3"/>
-      <c r="AI57" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="58" spans="1:35">
-      <c r="A58">
-        <v>10054</v>
-      </c>
-      <c r="B58" t="s">
-        <v>314</v>
-      </c>
-      <c r="C58">
-        <v>1</v>
-      </c>
-      <c r="D58">
-        <v>33</v>
-      </c>
-      <c r="E58" t="s">
-        <v>315</v>
-      </c>
-      <c r="H58" t="s">
-        <v>316</v>
-      </c>
-      <c r="I58" t="s">
-        <v>317</v>
-      </c>
-      <c r="J58">
-        <v>1000</v>
-      </c>
-      <c r="K58">
-        <v>1</v>
-      </c>
-      <c r="M58" t="s">
-        <v>318</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="S58">
-        <v>2</v>
-      </c>
-      <c r="T58">
-        <v>500</v>
-      </c>
-      <c r="U58">
-        <v>500</v>
-      </c>
-      <c r="V58">
-        <v>3000</v>
-      </c>
-      <c r="AC58">
+      <c r="AC58" t="n">
         <v>100120</v>
       </c>
       <c r="AF58" t="s">
         <v>199</v>
       </c>
-      <c r="AG58"/>
-      <c r="AH58"/>
+      <c r="AH58" t="n">
+        <v>1254003899</v>
+      </c>
       <c r="AI58" t="s">
-        <v>109</v>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="59" spans="1:35" s="51" customFormat="1">
+      <c r="A59" t="n">
+        <v>10055</v>
+      </c>
+      <c r="B59" s="54" t="s">
+        <v>320</v>
+      </c>
+      <c r="C59" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>36</v>
+      </c>
+      <c r="E59" s="55" t="s">
+        <v>321</v>
+      </c>
+      <c r="H59" s="55" t="s">
+        <v>321</v>
+      </c>
+      <c r="I59" s="51" t="s">
+        <v>322</v>
+      </c>
+      <c r="J59" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K59" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" s="51" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q59"/>
+      <c r="S59" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="T59" s="51" t="n">
+        <v>3500</v>
+      </c>
+      <c r="U59" s="51" t="n">
+        <v>3500</v>
+      </c>
+      <c r="V59" s="51" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>100120</v>
+      </c>
+      <c r="AF59" s="51" t="s">
+        <v>179</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>1254003899</v>
+      </c>
+      <c r="AI59" s="51" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="60" spans="1:35">
+      <c r="A60" t="n">
+        <v>10056</v>
+      </c>
+      <c r="B60" s="54" t="s">
+        <v>324</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="n">
+        <v>37</v>
+      </c>
+      <c r="E60" s="56" t="s">
+        <v>325</v>
+      </c>
+      <c r="H60" s="56" t="s">
+        <v>325</v>
+      </c>
+      <c r="I60" t="s">
+        <v>326</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1</v>
+      </c>
+      <c r="M60" t="s">
+        <v>327</v>
+      </c>
+      <c r="S60" t="n">
+        <v>2</v>
+      </c>
+      <c r="T60" s="51" t="n">
+        <v>3500</v>
+      </c>
+      <c r="U60" s="51" t="n">
+        <v>3500</v>
+      </c>
+      <c r="V60" s="51" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>100120</v>
+      </c>
+      <c r="AF60" t="s">
+        <v>179</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>1254003899</v>
+      </c>
+      <c r="AI60" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="61" spans="1:35" s="51" customFormat="1">
+      <c r="A61" t="n">
+        <v>10057</v>
+      </c>
+      <c r="B61" s="54" t="s">
+        <v>328</v>
+      </c>
+      <c r="C61" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>38</v>
+      </c>
+      <c r="E61" s="56" t="s">
+        <v>329</v>
+      </c>
+      <c r="H61" s="56" t="s">
+        <v>329</v>
+      </c>
+      <c r="I61" s="51" t="s">
+        <v>330</v>
+      </c>
+      <c r="J61" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K61" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" s="51" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q61"/>
+      <c r="S61" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="T61" s="51" t="n">
+        <v>3500</v>
+      </c>
+      <c r="U61" s="51" t="n">
+        <v>3500</v>
+      </c>
+      <c r="V61" s="51" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>100120</v>
+      </c>
+      <c r="AF61" s="51" t="s">
+        <v>179</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>1254003899</v>
+      </c>
+      <c r="AI61" s="51" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <conditionalFormatting sqref="B59:B61">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B59:B61">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1789641695" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.750000" right="0.750000" top="1.000000" bottom="1.000000" header="0.500000" footer="0.500000"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1" pageOrder="overThenDown"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1789641695" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1789641695" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1789641695" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1789641695" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
+  <extLst>
+    <ext uri="smNativeData">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1789641695" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+        <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+        <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+      </pm:sheetPrefs>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1:D38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultRowHeight="14.50"/>
   <cols>
-    <col min="1" max="1" width="18.25" customWidth="1"/>
-    <col min="2" max="2" width="18.625" customWidth="1"/>
+    <col min="1" max="1" width="18.245455" customWidth="1"/>
+    <col min="2" max="2" width="18.627273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1">
+      <c r="A1" t="n">
         <v>1160000399</v>
       </c>
-      <c r="B1">
+      <c r="B1" t="n">
         <v>1254003899</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2">
+      <c r="A2" t="n">
         <v>1160000499</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>1254003899</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3">
+      <c r="A3" t="n">
         <v>1160000499</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>1254003899</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4">
+      <c r="A4" t="n">
         <v>1160010599</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>1254003899</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5">
+      <c r="A5" t="n">
         <v>1160010699</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>1254003899</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6">
+      <c r="A6" t="n">
         <v>1160004399</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>1254003899</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7">
+      <c r="A7" t="n">
         <v>1160001999</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>1254003899</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="11" spans="2:2">
+      <c r="B11" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
       <c r="A17" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="24" ht="16.5" spans="1:4">
-      <c r="B24" s="1">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="B24" s="49" t="n">
         <v>2133004199</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="50" t="n">
         <v>2137002199</v>
       </c>
     </row>
-    <row r="25" ht="16.5" spans="1:4">
-      <c r="B25" s="1">
+    <row r="25" spans="2:2">
+      <c r="B25" s="49" t="n">
         <v>2133005199</v>
       </c>
     </row>
-    <row r="26" ht="16.5" spans="1:4">
-      <c r="B26" s="2">
+    <row r="26" spans="2:2">
+      <c r="B26" s="50" t="n">
         <v>2137001199</v>
       </c>
     </row>
-    <row r="27" ht="16.5" spans="1:4">
-      <c r="B27" s="2">
+    <row r="27" spans="2:2">
+      <c r="B27" s="50" t="n">
         <v>2137002199</v>
       </c>
     </row>
-    <row r="28" ht="16.5" spans="1:4">
-      <c r="B28" s="2">
+    <row r="28" spans="2:2">
+      <c r="B28" s="50" t="n">
         <v>2137003199</v>
       </c>
     </row>
-    <row r="29" ht="16.5" spans="1:4">
-      <c r="B29" s="2">
+    <row r="29" spans="2:2">
+      <c r="B29" s="50" t="n">
         <v>2137004199</v>
       </c>
     </row>
-    <row r="32" ht="16.5" spans="1:4">
-      <c r="B32" s="1">
+    <row r="32" spans="2:2">
+      <c r="B32" s="49" t="n">
         <v>2132001199</v>
       </c>
     </row>
-    <row r="33" ht="16.5" spans="2:2">
-      <c r="B33" s="1">
+    <row r="33" spans="2:2">
+      <c r="B33" s="49" t="n">
         <v>2132002199</v>
       </c>
     </row>
-    <row r="34" ht="16.5" spans="2:2">
-      <c r="B34" s="1">
+    <row r="34" spans="2:2">
+      <c r="B34" s="49" t="n">
         <v>2132003199</v>
       </c>
     </row>
-    <row r="35" ht="16.5" spans="2:2">
-      <c r="B35" s="1">
+    <row r="35" spans="2:2">
+      <c r="B35" s="49" t="n">
         <v>2132004199</v>
       </c>
     </row>
-    <row r="36" ht="16.5" spans="2:2">
-      <c r="B36" s="1">
+    <row r="36" spans="2:2">
+      <c r="B36" s="49" t="n">
         <v>2132005199</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B32:B36">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32:B36">
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26:B29">
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26:B29">
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25">
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25">
+    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B24">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24">
+    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D24">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B25">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+  <conditionalFormatting sqref="D24">
+    <cfRule type="duplicateValues" dxfId="11" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B26:B29">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B32:B36">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1789641695" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.750000" right="0.750000" top="1.000000" bottom="1.000000" header="0.500000" footer="0.500000"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1" pageOrder="overThenDown"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1789641695" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1789641695" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1789641695" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1789641695" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
+  <extLst>
+    <ext uri="smNativeData">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1789641695" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+        <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+        <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+      </pm:sheetPrefs>
+    </ext>
+  </extLst>
 </worksheet>
 </file>